--- a/sant_cugat_offer_candidates_500_600k.xlsx
+++ b/sant_cugat_offer_candidates_500_600k.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P101"/>
+  <dimension ref="A1:Q101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,30 +481,35 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>reactivation_events</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>budget_fit_score</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>quality_score</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>negotiation_model_score</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>final_score</t>
-        </is>
-      </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>final_score_reactivated</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>why_it_ranks</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>url</t>
         </is>
@@ -537,7 +542,7 @@
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>13.46</v>
+        <v>52.59361691111111</v>
       </c>
       <c r="I2" t="n">
         <v>2</v>
@@ -546,23 +551,26 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0.752</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>0.514</v>
+        <v>0.7521428571428572</v>
       </c>
       <c r="M2" t="n">
-        <v>0.676</v>
+        <v>0.5264867500323529</v>
       </c>
       <c r="N2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="O2" t="inlineStr">
+        <v>0.6954848725163563</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.6190571108497608</v>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>within target band, 1 price cut(s), strong size</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>https://www.idealista.com/inmueble/110766723/</t>
         </is>
@@ -571,33 +579,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>fincas_moragas_3994-2</t>
+          <t>qgat_homes_ref-1689</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>fincas_moragas</t>
+          <t>qgat_homes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Planta baixa en venda a Mira-sol</t>
+          <t>Xalet Independent en venda a Sant Cugat del Vallès - Can Barata</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>535000</v>
+        <v>549000</v>
       </c>
       <c r="E3" t="n">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>28.14</v>
+        <v>67.3172395962963</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
@@ -606,107 +614,115 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.745</v>
+        <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.53</v>
+        <v>0.855</v>
       </c>
       <c r="M3" t="n">
-        <v>0.483</v>
+        <v>0.3961839870247078</v>
       </c>
       <c r="N3" t="n">
-        <v>0.596</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.4426113163969075</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.609947728577339</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>https://fincasmoragas.com/ca/inmueble/3994-2/</t>
+          <t>within target band, long time online, 1 reactivation(s)</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>https://www.qgathomes.com/ca/venda/a-barcelona-sant_cugat_del_valles/ref-1689</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>idealista_101020918</t>
+          <t>yaencontre_inmueble-10424-111615630</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Casa o chalet independiente en La Floresta, Sant Cugat del Vallès</t>
+          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>550000</v>
+        <v>560000</v>
       </c>
       <c r="E4" t="n">
-        <v>226</v>
+        <v>118</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
       <c r="H4" t="n">
-        <v>13.46</v>
+        <v>46.1915683</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>0.863</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0.483</v>
+        <v>0.8414285714285714</v>
       </c>
       <c r="M4" t="n">
-        <v>0.24</v>
+        <v>0.423665794254466</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5669999999999999</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>within target band, strong size</t>
-        </is>
+        <v>0.6394852070034737</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.5969366453104015</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/101020918/</t>
+          <t>within target band, 1 price cut(s), strong size</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-10424-111615630</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-31679-111052607</t>
+          <t>idealista_111615630</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Piso en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
+          <t>Piso en Calle de Costa i Llobera, Coll Favà - Can Magí, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>615000</v>
+        <v>560000</v>
       </c>
       <c r="E5" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="F5" t="n">
         <v>3</v>
@@ -715,7 +731,7 @@
         <v>2</v>
       </c>
       <c r="H5" t="n">
-        <v>24.01</v>
+        <v>46.1915683</v>
       </c>
       <c r="I5" t="n">
         <v>2</v>
@@ -724,58 +740,61 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>0.626</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>0.38</v>
+        <v>0.8414285714285714</v>
       </c>
       <c r="M5" t="n">
-        <v>0.87</v>
+        <v>0.423665794254466</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5639999999999999</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>near target band, 1 price cut(s), strong size</t>
-        </is>
+        <v>0.6102370527191863</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.5925494221677584</v>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-31679-111052607</t>
+          <t>within target band, 1 price cut(s), strong size</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111615630/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>qgat_homes_ref-1726</t>
+          <t>fincas_moragas_3994-2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>qgat_homes</t>
+          <t>fincas_moragas</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cases en venda a Sant Cugat del Vallès - La Floresta</t>
+          <t>Planta baixa en venda a Mira-sol</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>549000</v>
+        <v>535000</v>
       </c>
       <c r="E6" t="n">
-        <v>214</v>
+        <v>132</v>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>12.02</v>
+        <v>67.27564237407408</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -784,25 +803,28 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.855</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.478</v>
+        <v>0.7450000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>0.229</v>
+        <v>0.5412276831515888</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.4310892042421718</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.5832318096615693</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>https://www.qgathomes.com/ca/venda/a-barcelona-sant_cugat_del_valles/ref-1726</t>
+          <t>within target band, long time online, strong size</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>https://fincasmoragas.com/ca/inmueble/3994-2/</t>
         </is>
       </c>
     </row>
@@ -833,7 +855,7 @@
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
-        <v>13.46</v>
+        <v>52.58798033703704</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -842,23 +864,26 @@
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.863</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.461</v>
+        <v>0.8628571428571428</v>
       </c>
       <c r="M7" t="n">
-        <v>0.24</v>
+        <v>0.4745850905828202</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5570000000000001</v>
-      </c>
-      <c r="O7" t="inlineStr">
+        <v>0.3099907108475541</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.5759700039163509</v>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>within target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>https://www.idealista.com/inmueble/110895318/</t>
         </is>
@@ -867,60 +892,63 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>organ_ref-2069</t>
+          <t>yaencontre_inmueble-60224-111418252</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>organ</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PISO EN VENTA - COLL FAVÀ - COLL FAVA</t>
+          <t>Piso en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>585000</v>
+        <v>560000</v>
       </c>
       <c r="E8" t="n">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="F8" t="n">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="G8" t="n">
-        <v>91</v>
+        <v>2</v>
       </c>
       <c r="H8" t="n">
-        <v>14.95</v>
+        <v>63.13662617037037</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>0.788</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0.438</v>
+        <v>0.8414285714285714</v>
       </c>
       <c r="M8" t="n">
-        <v>0.337</v>
+        <v>0.2951040597456136</v>
       </c>
       <c r="N8" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>within target band, good profile match</t>
-        </is>
+        <v>0.8175355684221857</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.5696482710294903</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>https://www.organ.es/es/ref-2069</t>
+          <t>within target band, long time online, 1 price cut(s)</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-60224-111418252</t>
         </is>
       </c>
     </row>
@@ -941,7 +969,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>545000</v>
+        <v>525000</v>
       </c>
       <c r="E9" t="n">
         <v>231</v>
@@ -951,32 +979,35 @@
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>13.46</v>
+        <v>52.59361691111111</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>0.824</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.447</v>
+        <v>0.6664285714285714</v>
       </c>
       <c r="M9" t="n">
-        <v>0.237</v>
+        <v>0.4596218918761275</v>
       </c>
       <c r="N9" t="n">
-        <v>0.537</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.6763687595953585</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5598207392002821</v>
       </c>
       <c r="P9" t="inlineStr">
+        <is>
+          <t>within target band, 1 price cut(s), strong size</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
         <is>
           <t>https://www.idealista.com/inmueble/109506329/</t>
         </is>
@@ -985,33 +1016,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>qgat_homes_ref-1689</t>
+          <t>idealista_111906991</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>qgat_homes</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Xalet Independent en venda a Sant Cugat del Vallès - Can Barata</t>
+          <t>Casa o chalet independiente en La Floresta, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>549000</v>
+        <v>550000</v>
       </c>
       <c r="E10" t="n">
-        <v>174</v>
+        <v>226</v>
       </c>
       <c r="F10" t="n">
-        <v>2</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>28.19</v>
+        <v>14.05390626296296</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -1020,116 +1049,122 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.855</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0.289</v>
+        <v>0.8628571428571428</v>
       </c>
       <c r="M10" t="n">
-        <v>0.51</v>
+        <v>0.496885556776784</v>
       </c>
       <c r="N10" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="O10" t="inlineStr">
+        <v>0.09250761091650295</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.552713734728158</v>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>within target band, strong size</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>https://www.qgathomes.com/ca/venda/a-barcelona-sant_cugat_del_valles/ref-1689</t>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111906991/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-81822-107768818</t>
+          <t>idealista_111542558</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
+          <t>Casa o chalet independiente en Calle de Maria Antònia, Les Planes, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>555000</v>
+        <v>525000</v>
       </c>
       <c r="E11" t="n">
-        <v>116</v>
+        <v>231</v>
       </c>
       <c r="F11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>24.01</v>
+        <v>47.14251737407407</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0.852</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>0.321</v>
+        <v>0.6664285714285714</v>
       </c>
       <c r="M11" t="n">
-        <v>0.406</v>
+        <v>0.4596218918761275</v>
       </c>
       <c r="N11" t="n">
-        <v>0.524</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.6180109469329526</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.5510670673009213</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-81822-107768818</t>
+          <t>within target band, 1 price cut(s), strong size</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111542558/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>idealista_111542558</t>
+          <t>organ_ref-2069</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>organ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Casa o chalet independiente en Calle de Maria Antònia, Les Planes, Sant Cugat del Vallès</t>
+          <t>PISO EN VENTA - COLL FAVÀ - COLL FAVA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>545000</v>
+        <v>585000</v>
       </c>
       <c r="E12" t="n">
-        <v>231</v>
+        <v>91</v>
       </c>
       <c r="F12" t="n">
-        <v>4</v>
-      </c>
-      <c r="G12" t="inlineStr"/>
+        <v>91</v>
+      </c>
+      <c r="G12" t="n">
+        <v>91</v>
+      </c>
       <c r="H12" t="n">
-        <v>8.01</v>
+        <v>54.08014468888889</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -1138,32 +1173,35 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.824</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0.447</v>
+        <v>0.7878571428571428</v>
       </c>
       <c r="M12" t="n">
-        <v>0.142</v>
+        <v>0.4384706175208889</v>
       </c>
       <c r="N12" t="n">
-        <v>0.518</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.3661428995839819</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.5444747535408039</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111542558/</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>https://www.organ.es/es/ref-2069</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>idealista_110966836</t>
+          <t>idealista_111418252</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1173,17 +1211,21 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chalet pareado en Calle Riba, 2, Viladecavalls</t>
+          <t>Piso en Can Matas, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>514900</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
+        <v>560000</v>
+      </c>
+      <c r="E13" t="n">
+        <v>73</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2</v>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>13.46</v>
+        <v>52.58798033703704</v>
       </c>
       <c r="I13" t="n">
         <v>2</v>
@@ -1192,25 +1234,28 @@
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0.587</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0.347</v>
+        <v>0.8414285714285714</v>
       </c>
       <c r="M13" t="n">
-        <v>0.759</v>
+        <v>0.2734432513097613</v>
       </c>
       <c r="N13" t="n">
-        <v>0.513</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>within target band, 1 price cut(s)</t>
-        </is>
+        <v>0.6816918282867408</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.5401741704661156</v>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/110966836/</t>
+          <t>within target band, 1 price cut(s), good profile match</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111418252/</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1282,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>13.46</v>
+        <v>52.59361691111111</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
@@ -1246,23 +1291,26 @@
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.863</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0.362</v>
+        <v>0.8628571428571428</v>
       </c>
       <c r="M14" t="n">
-        <v>0.238</v>
+        <v>0.368731258211852</v>
       </c>
       <c r="N14" t="n">
-        <v>0.513</v>
-      </c>
-      <c r="O14" t="inlineStr">
+        <v>0.3092347950079624</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.5313980069446055</v>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>within target band</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>https://www.idealista.com/inmueble/111315640/</t>
         </is>
@@ -1271,7 +1319,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-70970-111266709</t>
+          <t>yaencontre_inmueble-81822-107768818</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1285,10 +1333,10 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>599000</v>
+        <v>555000</v>
       </c>
       <c r="E15" t="n">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
@@ -1297,7 +1345,7 @@
         <v>2</v>
       </c>
       <c r="H15" t="n">
-        <v>24.01</v>
+        <v>63.13662617037037</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
@@ -1306,118 +1354,122 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.752</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0.366</v>
+        <v>0.8521428571428571</v>
       </c>
       <c r="M15" t="n">
-        <v>0.406</v>
+        <v>0.3307897453490256</v>
       </c>
       <c r="N15" t="n">
-        <v>0.509</v>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>within target band, good profile match</t>
-        </is>
+        <v>0.3926435492525839</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.5244381703931974</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-70970-111266709</t>
+          <t>within target band, long time online, strong size</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-81822-107768818</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tecnocasa_casa-en-venta-631866</t>
+          <t>qgat_homes_ref-1750</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>tecnocasa</t>
+          <t>qgat_homes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Casa en venta</t>
+          <t>Àtic en venda a Sant Cugat del Vallès - Volpelleres</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>654000</v>
+        <v>619000</v>
       </c>
       <c r="E16" t="n">
-        <v>165</v>
+        <v>104</v>
       </c>
       <c r="F16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>28.14</v>
+        <v>30.22449654074074</v>
       </c>
       <c r="I16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.32</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>0.433</v>
+        <v>0.595</v>
       </c>
       <c r="M16" t="n">
-        <v>0.959</v>
+        <v>0.4717427133950886</v>
       </c>
       <c r="N16" t="n">
-        <v>0.499</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>near target band, 1 price cut(s), strong size</t>
-        </is>
+        <v>0.2245539641568935</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.5231737908168967</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>https://santcugat1.tecnocasa.es/sant-cugat-del-valles/casa-en-venta-631866</t>
+          <t>near target band, 1 reactivation(s), strong size</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>https://www.qgathomes.com/ca/venda/a-barcelona-sant_cugat_del_valles/ref-1750</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-60296-111393834</t>
+          <t>idealista_111136628</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Piso en Torreblanca, Sant Cugat del Vallès</t>
+          <t>Casa o chalet independiente en Calle Priorat, Can Barata, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>550000</v>
+        <v>549000</v>
       </c>
       <c r="E17" t="n">
-        <v>100</v>
+        <v>174</v>
       </c>
       <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="G17" t="n">
-        <v>2</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>24.01</v>
+        <v>52.58798033703704</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -1426,56 +1478,61 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.863</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.253</v>
+        <v>0.855</v>
       </c>
       <c r="M17" t="n">
-        <v>0.406</v>
+        <v>0.3442496363845968</v>
       </c>
       <c r="N17" t="n">
-        <v>0.497</v>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.3079910303428114</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.5183363039345286</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-60296-111393834</t>
+          <t>within target band, strong size</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111136628/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>idealista_111136628</t>
+          <t>tecnocasa_piso-en-venta-661224</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>tecnocasa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Casa o chalet independiente en Calle Priorat, Can Barata, Sant Cugat del Vallès</t>
+          <t>Piso en venta</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>549000</v>
+        <v>620000</v>
       </c>
       <c r="E18" t="n">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="F18" t="n">
-        <v>2</v>
-      </c>
-      <c r="G18" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
       <c r="H18" t="n">
-        <v>13.46</v>
+        <v>40.21367478148148</v>
       </c>
       <c r="I18" t="n">
         <v>1</v>
@@ -1484,32 +1541,35 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.855</v>
+        <v>3</v>
       </c>
       <c r="L18" t="n">
-        <v>0.332</v>
+        <v>0.5871428571428572</v>
       </c>
       <c r="M18" t="n">
-        <v>0.235</v>
+        <v>0.4223845621339317</v>
       </c>
       <c r="N18" t="n">
-        <v>0.496</v>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>within target band, strong size</t>
-        </is>
+        <v>0.2627818145789492</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.5100505370947024</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111136628/</t>
+          <t>near target band, 3 reactivation(s), strong size</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>https://santcugat1.tecnocasa.es/sant-cugat-del-valles/piso-en-venta-661224</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>idealista_111615630</t>
+          <t>idealista_110966836</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1519,57 +1579,54 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Piso en Calle de Costa i Llobera, Coll Favà - Can Magí, Sant Cugat del Vallès</t>
+          <t>Chalet pareado en Calle Riba, 2, Viladecavalls</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>575000</v>
-      </c>
-      <c r="E19" t="n">
-        <v>118</v>
-      </c>
-      <c r="F19" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" t="n">
-        <v>2</v>
-      </c>
+        <v>514900</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
-        <v>7.06</v>
+        <v>52.59361691111111</v>
       </c>
       <c r="I19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8090000000000001</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>0.414</v>
+        <v>0.5870714285714286</v>
       </c>
       <c r="M19" t="n">
-        <v>0.123</v>
+        <v>0.3537048961731877</v>
       </c>
       <c r="N19" t="n">
-        <v>0.494</v>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.7735182774223255</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.5037201715362353</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111615630/</t>
+          <t>within target band, 1 price cut(s)</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110966836/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-60224-111418252</t>
+          <t>yaencontre_inmueble-60296-111393834</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1579,14 +1636,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Piso en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
+          <t>Piso en Torreblanca, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>580000</v>
+        <v>550000</v>
       </c>
       <c r="E20" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="F20" t="n">
         <v>2</v>
@@ -1595,7 +1652,7 @@
         <v>2</v>
       </c>
       <c r="H20" t="n">
-        <v>24.01</v>
+        <v>63.13662617037037</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
@@ -1604,32 +1661,35 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.799</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>0.295</v>
+        <v>0.8628571428571428</v>
       </c>
       <c r="M20" t="n">
-        <v>0.405</v>
+        <v>0.2618780242102213</v>
       </c>
       <c r="N20" t="n">
-        <v>0.493</v>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>within target band, good profile match</t>
-        </is>
+        <v>0.3919601483931001</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.4989284516716913</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-60224-111418252</t>
+          <t>within target band, long time online, strong size</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-60296-111393834</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-10424-111615630</t>
+          <t>yaencontre_inmueble-55669-108652532</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1639,14 +1699,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
+          <t>Piso en calle Can Vulpelleres en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>575000</v>
+        <v>550000</v>
       </c>
       <c r="E21" t="n">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="F21" t="n">
         <v>3</v>
@@ -1655,7 +1715,7 @@
         <v>2</v>
       </c>
       <c r="H21" t="n">
-        <v>7.06</v>
+        <v>63.13662617037037</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
@@ -1664,32 +1724,35 @@
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8090000000000001</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.414</v>
+        <v>0.8628571428571428</v>
       </c>
       <c r="M21" t="n">
-        <v>0.111</v>
+        <v>0.2437447303998297</v>
       </c>
       <c r="N21" t="n">
-        <v>0.492</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.3915460448355758</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.4912503527376981</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-10424-111615630</t>
+          <t>within target band, long time online, good profile match</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-55669-108652532</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-55669-108652532</t>
+          <t>yaencontre_inmueble-50971-110658936</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1699,14 +1762,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Piso en calle Can Vulpelleres en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
+          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>550000</v>
+        <v>525000</v>
       </c>
       <c r="E22" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
         <v>3</v>
@@ -1715,7 +1778,7 @@
         <v>2</v>
       </c>
       <c r="H22" t="n">
-        <v>24.01</v>
+        <v>63.13662617037037</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
@@ -1724,25 +1787,28 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>0.863</v>
+        <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.237</v>
+        <v>0.6664285714285714</v>
       </c>
       <c r="M22" t="n">
-        <v>0.408</v>
+        <v>0.3970142661147983</v>
       </c>
       <c r="N22" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>within target band, good profile match</t>
-        </is>
+        <v>0.3911485244879773</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.4907425011144166</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-55669-108652532</t>
+          <t>within target band, long time online, strong size</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-50971-110658936</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1841,7 @@
         <v>2</v>
       </c>
       <c r="H23" t="n">
-        <v>24.01</v>
+        <v>63.13662617037037</v>
       </c>
       <c r="I23" t="n">
         <v>1</v>
@@ -1784,23 +1850,26 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0.697</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>0.363</v>
+        <v>0.6971428571428572</v>
       </c>
       <c r="M23" t="n">
-        <v>0.406</v>
+        <v>0.3722867209360883</v>
       </c>
       <c r="N23" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>near target band, good profile match</t>
-        </is>
+        <v>0.3908320331025645</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.4904451727172608</v>
       </c>
       <c r="P23" t="inlineStr">
+        <is>
+          <t>near target band, long time online, good profile match</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
         <is>
           <t>https://www.yaencontre.com/venta/piso/inmueble-77186-108411479</t>
         </is>
@@ -1809,7 +1878,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-50971-110658936</t>
+          <t>yaencontre_inmueble-51945-111748909</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1819,23 +1888,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
+          <t>Ático en Parc Central - El Colomer - Pla de la Pagesa, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>525000</v>
+        <v>560000</v>
       </c>
       <c r="E24" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>2</v>
       </c>
       <c r="H24" t="n">
-        <v>24.01</v>
+        <v>31.1259895962963</v>
       </c>
       <c r="I24" t="n">
         <v>1</v>
@@ -1844,52 +1913,61 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0.666</v>
+        <v>0</v>
       </c>
       <c r="L24" t="n">
-        <v>0.386</v>
+        <v>0.8414285714285714</v>
       </c>
       <c r="M24" t="n">
-        <v>0.406</v>
+        <v>0.3181681580312723</v>
       </c>
       <c r="N24" t="n">
-        <v>0.488</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.2107127610501131</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.4883117712036561</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-50971-110658936</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-51945-111748909</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>idealista_111058444</t>
+          <t>qgat_homes_ref-1699</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>qgat_homes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Piso en Calle Arenys y Pluto, 109, La Teixonera, Barcelona</t>
+          <t>Cases en venda a Sant Cugat del Vallès - Valldoreix</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>560000</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
+        <v>589000</v>
+      </c>
+      <c r="E25" t="n">
+        <v>60</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
       <c r="H25" t="n">
-        <v>5.1</v>
+        <v>67.3172395962963</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -1898,58 +1976,59 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.841</v>
+        <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>0.367</v>
+        <v>0.7792857142857144</v>
       </c>
       <c r="M25" t="n">
-        <v>0.093</v>
+        <v>0.1529996660381557</v>
       </c>
       <c r="N25" t="n">
-        <v>0.478</v>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>within target band</t>
-        </is>
+        <v>0.4446338338347674</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.4831279770929518</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111058444/</t>
+          <t>within target band, long time online, 1 reactivation(s)</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>https://www.qgathomes.com/ca/venda/a-barcelona-sant_cugat_del_valles/ref-1699</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-35254-111405695</t>
+          <t>idealista_111969057</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ático en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
+          <t>Casa o chalet independiente en Can Barata, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>615000</v>
+        <v>549900</v>
       </c>
       <c r="E26" t="n">
-        <v>111</v>
+        <v>174</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>24.01</v>
+        <v>7.055584503703704</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -1958,58 +2037,59 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0.626</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>0.395</v>
+        <v>0.8620714285714285</v>
       </c>
       <c r="M26" t="n">
-        <v>0.406</v>
+        <v>0.3440552729249272</v>
       </c>
       <c r="N26" t="n">
-        <v>0.478</v>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.04843959322916033</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.481655527142991</v>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-35254-111405695</t>
+          <t>within target band, strong size</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111969057/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-68054-111045661</t>
+          <t>idealista_111713403</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ático en Parc Central - El Colomer - Pla de la Pagesa, Sant Cugat del Vallès</t>
+          <t>Casa o chalet en Calle de Can Barata, 42, Can Barata, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>560000</v>
+        <v>545000</v>
       </c>
       <c r="E27" t="n">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>24.01</v>
+        <v>35.25251737407407</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
@@ -2018,176 +2098,185 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>0.841</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>0.207</v>
+        <v>0.8235714285714285</v>
       </c>
       <c r="M27" t="n">
-        <v>0.405</v>
+        <v>0.3163999911217643</v>
       </c>
       <c r="N27" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>within target band, good profile match</t>
-        </is>
+        <v>0.2067840558072198</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.4810869781723716</v>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-68054-111045661</t>
+          <t>within target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111713403/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>idealista_111496873</t>
+          <t>qgat_homes_ref-1731</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>qgat_homes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Ático en Can Matas, Sant Cugat del Vallès</t>
+          <t>Cases en venda a Sant Cugat del Vallès - Mas Gener</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>565000</v>
+        <v>610000</v>
       </c>
       <c r="E28" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="F28" t="n">
         <v>2</v>
       </c>
-      <c r="G28" t="inlineStr"/>
+      <c r="G28" t="n">
+        <v>1</v>
+      </c>
       <c r="H28" t="n">
-        <v>13.46</v>
+        <v>42.07772570740741</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K28" t="n">
-        <v>0.831</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>0.291</v>
+        <v>0.6657142857142857</v>
       </c>
       <c r="M28" t="n">
-        <v>0.235</v>
+        <v>0.1695865794302922</v>
       </c>
       <c r="N28" t="n">
-        <v>0.469</v>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>within target band, good profile match</t>
-        </is>
+        <v>0.6193610876774138</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.4788249973654747</v>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111496873/</t>
+          <t>near target band, 1 price cut(s), 1 reactivation(s)</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>https://www.qgathomes.com/ca/venda/a-barcelona-sant_cugat_del_valles/ref-1731</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>fincas_cano_pujol_ref-6067</t>
+          <t>amat_casa-amb-encant-a-zona-mas-gener-de-mirasol</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>fincas_cano_pujol</t>
+          <t>amat</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sant Cugat del Vallès 6067</t>
+          <t>Casa amb encant, a zona Mas Gener de Mirasol</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>525000</v>
+        <v>615000</v>
       </c>
       <c r="E29" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>67.3172395962963</v>
+      </c>
+      <c r="I29" t="n">
         <v>3</v>
       </c>
-      <c r="G29" t="n">
-        <v>2</v>
-      </c>
-      <c r="H29" t="n">
-        <v>28.14</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1</v>
-      </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.666</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0.304</v>
+        <v>0.6264285714285714</v>
       </c>
       <c r="M29" t="n">
-        <v>0.489</v>
+        <v>0.1805301047188912</v>
       </c>
       <c r="N29" t="n">
-        <v>0.468</v>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.4779468746549391</v>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>https://www.fincascanopujol.es/es/venta/en-barcelona-sant_cugat_del_valles/ref-6067</t>
+          <t>near target band, long time online, 2 price cut(s)</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>https://www.amatimmobiliaris.com/ca/venda/casa/barcelona/sant-cugat-del-valles/casa-amb-encant-a-zona-mas-gener-de-mirasol</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>qgat_homes_ref-1716</t>
+          <t>idealista_111748909</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>qgat_homes</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Àtic en venda a Sant Cugat del Vallès - Can Mates</t>
+          <t>Ático en Parc Central - Colomer, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>615000</v>
+        <v>560000</v>
       </c>
       <c r="E30" t="n">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="F30" t="n">
-        <v>3</v>
-      </c>
-      <c r="G30" t="n">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="n">
-        <v>28.19</v>
+        <v>31.1259895962963</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
@@ -2196,54 +2285,59 @@
         <v>0</v>
       </c>
       <c r="K30" t="n">
-        <v>0.626</v>
+        <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0.309</v>
+        <v>0.8414285714285714</v>
       </c>
       <c r="M30" t="n">
-        <v>0.511</v>
+        <v>0.29650734959542</v>
       </c>
       <c r="N30" t="n">
-        <v>0.461</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.1841131154111748</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.4752242848147573</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>https://www.qgathomes.com/ca/venda/a-barcelona-sant_cugat_del_valles/ref-1716</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111748909/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>aproperties_parcela-de-635-m2-en-venta-en-valldoreix-sant-cugat-del-valles</t>
+          <t>idealista_111393834</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>aproperties</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Terreno en venta en Valldoreix</t>
+          <t>Piso en Torreblanca, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>490000</v>
+        <v>550000</v>
       </c>
       <c r="E31" t="n">
-        <v>635</v>
-      </c>
-      <c r="F31" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="F31" t="n">
+        <v>2</v>
+      </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>28.14</v>
+        <v>50.2454108925926</v>
       </c>
       <c r="I31" t="n">
         <v>1</v>
@@ -2252,116 +2346,124 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.391</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0.494</v>
+        <v>0.8628571428571428</v>
       </c>
       <c r="M31" t="n">
-        <v>0.486</v>
+        <v>0.2342418203437889</v>
       </c>
       <c r="N31" t="n">
-        <v>0.457</v>
-      </c>
-      <c r="O31" t="inlineStr">
+        <v>0.2916330682936267</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.4722721840328686</v>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>within target band, strong size</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>https://www.aproperties.es/sant-cugat-del-valles/valldoreix/parcela-de-635-m2-en-venta-en-valldoreix-sant-cugat-del-valles</t>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111393834/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-625-109332513</t>
+          <t>qgat_homes_ref-1739</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>qgat_homes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Piso en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
+          <t>Casa en venda a Mas Gener. Mirasol.</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>625000</v>
+        <v>695000</v>
       </c>
       <c r="E32" t="n">
-        <v>115</v>
+        <v>157</v>
       </c>
       <c r="F32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G32" t="n">
         <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>24.01</v>
+        <v>37.23014468888889</v>
       </c>
       <c r="I32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K32" t="n">
-        <v>0.548</v>
+        <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>0.406</v>
+        <v>0.1228571428571429</v>
       </c>
       <c r="M32" t="n">
-        <v>0.406</v>
+        <v>0.5988459011414995</v>
       </c>
       <c r="N32" t="n">
-        <v>0.456</v>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.5567365124915293</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.4705773690634419</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-625-109332513</t>
+          <t>near target band, 1 price cut(s), 1 reactivation(s)</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>https://www.qgathomes.com/ca/venda/a-barcelona-sant_cugat_del_valles/ref-1739</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>idealista_111418252</t>
+          <t>yaencontre_inmueble-59451-111543497</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Piso en Can Matas, Sant Cugat del Vallès</t>
+          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>580000</v>
+        <v>585000</v>
       </c>
       <c r="E33" t="n">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
-      </c>
-      <c r="G33" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
       <c r="H33" t="n">
-        <v>13.46</v>
+        <v>54.08014468888889</v>
       </c>
       <c r="I33" t="n">
         <v>1</v>
@@ -2370,118 +2472,122 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.799</v>
+        <v>0</v>
       </c>
       <c r="L33" t="n">
-        <v>0.276</v>
+        <v>0.7878571428571428</v>
       </c>
       <c r="M33" t="n">
-        <v>0.235</v>
+        <v>0.2705066364008599</v>
       </c>
       <c r="N33" t="n">
-        <v>0.451</v>
-      </c>
-      <c r="O33" t="inlineStr">
+        <v>0.3382908569236652</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.4697520750713443</v>
+      </c>
+      <c r="P33" t="inlineStr">
         <is>
           <t>within target band, good profile match</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/111418252/</t>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-59451-111543497</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-81822-111056938</t>
+          <t>qgat_homes_ref-1683</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>qgat_homes</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Piso en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
+          <t>Cases en venda a Sant Cugat del Vallès - La Floresta</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>624000</v>
+        <v>620000</v>
       </c>
       <c r="E34" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G34" t="n">
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>24.01</v>
+        <v>67.3172395962963</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>0.556</v>
+        <v>1</v>
       </c>
       <c r="L34" t="n">
-        <v>0.178</v>
+        <v>0.5871428571428572</v>
       </c>
       <c r="M34" t="n">
-        <v>0.872</v>
+        <v>0.2621028834473952</v>
       </c>
       <c r="N34" t="n">
-        <v>0.449</v>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>near target band, 1 price cut(s), good profile match</t>
-        </is>
+        <v>0.4433576993461853</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.4653527653744022</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-81822-111056938</t>
+          <t>near target band, long time online, 1 reactivation(s)</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>https://www.qgathomes.com/ca/venda/a-barcelona-sant_cugat_del_valles/ref-1683</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>qgat_homes_ref-1707</t>
+          <t>idealista_108652532</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>qgat_homes</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Àtic en venda a Sant Cugat del Vallès - Parc Central</t>
+          <t>Piso en Can Vulpelleres, 24, Coll Favà - Can Magí, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>619000</v>
+        <v>550000</v>
       </c>
       <c r="E35" t="n">
-        <v>108</v>
+        <v>80</v>
       </c>
       <c r="F35" t="n">
         <v>3</v>
       </c>
-      <c r="G35" t="n">
-        <v>2</v>
-      </c>
+      <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
-        <v>28.19</v>
+        <v>50.2454108925926</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
@@ -2490,58 +2596,61 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>0.595</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0.301</v>
+        <v>0.8628571428571428</v>
       </c>
       <c r="M35" t="n">
-        <v>0.511</v>
+        <v>0.2135601961291794</v>
       </c>
       <c r="N35" t="n">
-        <v>0.446</v>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.2911211250237623</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.463509110372253</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>https://www.qgathomes.com/ca/venda/a-barcelona-sant_cugat_del_valles/ref-1707</t>
+          <t>within target band</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/108652532/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>qgat_homes_ref-1699</t>
+          <t>fincas_cano_pujol_ref-6067</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>qgat_homes</t>
+          <t>fincas_cano_pujol</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cases en venda a Sant Cugat del Vallès - Valldoreix</t>
+          <t>Sant Cugat del Vallès 6067</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>589000</v>
+        <v>525000</v>
       </c>
       <c r="E36" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H36" t="n">
-        <v>28.19</v>
+        <v>67.27564237407408</v>
       </c>
       <c r="I36" t="n">
         <v>1</v>
@@ -2550,56 +2659,61 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>0.779</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>0.153</v>
+        <v>0.6664285714285714</v>
       </c>
       <c r="M36" t="n">
-        <v>0.509</v>
+        <v>0.3154764805260461</v>
       </c>
       <c r="N36" t="n">
-        <v>0.444</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>within target band, good profile match</t>
-        </is>
+        <v>0.4346944098654874</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.4630285139737672</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>https://www.qgathomes.com/ca/venda/a-barcelona-sant_cugat_del_valles/ref-1699</t>
+          <t>within target band, long time online, strong size</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>https://www.fincascanopujol.es/es/venta/en-barcelona-sant_cugat_del_valles/ref-6067</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>idealista_111393834</t>
+          <t>yaencontre_inmueble-625-109332513</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Piso en Torreblanca, Sant Cugat del Vallès</t>
+          <t>Piso en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>550000</v>
+        <v>625000</v>
       </c>
       <c r="E37" t="n">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
-      </c>
-      <c r="G37" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G37" t="n">
+        <v>2</v>
+      </c>
       <c r="H37" t="n">
-        <v>11.11</v>
+        <v>63.13662617037037</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
@@ -2608,42 +2722,45 @@
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>0.863</v>
+        <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0.227</v>
+        <v>0.5478571428571428</v>
       </c>
       <c r="M37" t="n">
-        <v>0.196</v>
+        <v>0.4177039724911084</v>
       </c>
       <c r="N37" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>within target band, strong size</t>
-        </is>
+        <v>0.3890699291977021</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.4599918170703542</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111393834/</t>
+          <t>near target band, long time online, strong size</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-625-109332513</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-59451-111543497</t>
+          <t>idealista_111543497</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
+          <t>Piso en Calle d'Aribau, Coll Favà - Can Magí, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -2655,11 +2772,9 @@
       <c r="F38" t="n">
         <v>3</v>
       </c>
-      <c r="G38" t="n">
-        <v>2</v>
-      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="n">
-        <v>14.95</v>
+        <v>50.2454108925926</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -2668,92 +2783,96 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0.788</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>0.261</v>
+        <v>0.7878571428571428</v>
       </c>
       <c r="M38" t="n">
-        <v>0.25</v>
+        <v>0.2488458279650076</v>
       </c>
       <c r="N38" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="O38" t="inlineStr">
+        <v>0.2898278489299715</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.4533850843292322</v>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t>within target band, good profile match</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-59451-111543497</t>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111543497/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-51945-110670002</t>
+          <t>idealista_106551307</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
+          <t>Casa o chalet independiente en Calle d'Astúries, Mirasol, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>655000</v>
+        <v>699000</v>
       </c>
       <c r="E39" t="n">
-        <v>94</v>
+        <v>421</v>
       </c>
       <c r="F39" t="n">
-        <v>3</v>
-      </c>
-      <c r="G39" t="n">
-        <v>2</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
-        <v>24.01</v>
+        <v>50.2454108925926</v>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.312</v>
+        <v>1</v>
       </c>
       <c r="L39" t="n">
-        <v>0.354</v>
+        <v>0.1114285714285714</v>
       </c>
       <c r="M39" t="n">
-        <v>0.847</v>
+        <v>0.656270634075627</v>
       </c>
       <c r="N39" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>near target band, 1 price cut(s), good profile match</t>
-        </is>
+        <v>0.2918357424329009</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.4511892128155526</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-51945-110670002</t>
+          <t>near target band, 1 reactivation(s), strong size</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/106551307/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>idealista_111405695</t>
+          <t>idealista_111826265</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2763,21 +2882,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ático en Calle de Bonaventura de Gayolà, Can Matas, Sant Cugat del Vallès</t>
+          <t>Piso en Plaza Eivissa, 1, Horta, Barcelona</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>615000</v>
-      </c>
-      <c r="E40" t="n">
-        <v>111</v>
-      </c>
-      <c r="F40" t="n">
-        <v>3</v>
-      </c>
+        <v>530098</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
-        <v>13.46</v>
+        <v>21.35008681851852</v>
       </c>
       <c r="I40" t="n">
         <v>1</v>
@@ -2786,32 +2901,35 @@
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0.626</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0.38</v>
+        <v>0.7064842857142857</v>
       </c>
       <c r="M40" t="n">
-        <v>0.237</v>
+        <v>0.3602075323770542</v>
       </c>
       <c r="N40" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.1306121419492794</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.4494216012780451</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111405695/</t>
+          <t>within target band</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111826265/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>idealista_111052607</t>
+          <t>idealista_110439991</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2821,23 +2939,23 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Piso en Dolors Bigas, Volpelleres, Sant Cugat del Vallès</t>
+          <t>Casa o chalet en La Floresta, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>615000</v>
+        <v>620000</v>
       </c>
       <c r="E41" t="n">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>13.46</v>
+        <v>50.2454108925926</v>
       </c>
       <c r="I41" t="n">
         <v>1</v>
@@ -2846,56 +2964,61 @@
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0.626</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
-        <v>0.38</v>
+        <v>0.5871428571428572</v>
       </c>
       <c r="M41" t="n">
-        <v>0.236</v>
+        <v>0.2638164159605763</v>
       </c>
       <c r="N41" t="n">
-        <v>0.438</v>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.2828600454405706</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.4419978009440961</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111052607/</t>
+          <t>near target band, 1 reactivation(s), good profile match</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110439991/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>idealista_108652532</t>
+          <t>aproperties_piso-de-79-m2-con-terraza-y-aparcamiento-en-venta-en-centre-sant-cugat-del-valles</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>aproperties</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Piso en Can Vulpelleres, 24, Coll Favà - Can Magí, Sant Cugat del Vallès</t>
+          <t>Piso en venta en Sant Cugat</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>550000</v>
+        <v>590000</v>
       </c>
       <c r="E42" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F42" t="n">
         <v>3</v>
       </c>
-      <c r="G42" t="inlineStr"/>
+      <c r="G42" t="n">
+        <v>2</v>
+      </c>
       <c r="H42" t="n">
-        <v>11.11</v>
+        <v>28.07310765185185</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
@@ -2904,58 +3027,61 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>0.863</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0.208</v>
+        <v>0.7771428571428571</v>
       </c>
       <c r="M42" t="n">
-        <v>0.198</v>
+        <v>0.2514335787695359</v>
       </c>
       <c r="N42" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>within target band</t>
-        </is>
+        <v>0.2104928647308706</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.4390359777515547</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/108652532/</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>https://www.aproperties.es/sant-cugat-del-valles/centre/piso-de-79-m2-con-terraza-y-aparcamiento-en-venta-en-centre-sant-cugat-del-valles</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>tecnocasa_casa-en-venta-659614</t>
+          <t>yaencontre_inmueble-54742-111945069</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>tecnocasa</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Casa en venta</t>
+          <t>Piso en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>550000</v>
+        <v>589000</v>
       </c>
       <c r="E43" t="n">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="F43" t="n">
         <v>3</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H43" t="n">
-        <v>14.95</v>
+        <v>0.9851794111111111</v>
       </c>
       <c r="I43" t="n">
         <v>1</v>
@@ -2964,56 +3090,61 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0.863</v>
+        <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0.177</v>
+        <v>0.7792857142857144</v>
       </c>
       <c r="M43" t="n">
-        <v>0.256</v>
+        <v>0.3053266235964196</v>
       </c>
       <c r="N43" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>within target band</t>
-        </is>
+        <v>0.03597349665040904</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.4362002942239196</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>https://santcugat1.tecnocasa.es/sant-cugat-del-valles/casa-en-venta-659614</t>
+          <t>within target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-54742-111945069</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>idealista_111542946</t>
+          <t>yaencontre_inmueble-60000-111780986</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Chalet adosado en Sant Domènec, Sant Cugat del Vallès</t>
+          <t>Piso en Torreblanca, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>550000</v>
+        <v>590000</v>
       </c>
       <c r="E44" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="F44" t="n">
         <v>3</v>
       </c>
-      <c r="G44" t="inlineStr"/>
+      <c r="G44" t="n">
+        <v>2</v>
+      </c>
       <c r="H44" t="n">
-        <v>11.11</v>
+        <v>28.07310765185185</v>
       </c>
       <c r="I44" t="n">
         <v>1</v>
@@ -3022,32 +3153,35 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0.863</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>0.202</v>
+        <v>0.7771428571428571</v>
       </c>
       <c r="M44" t="n">
-        <v>0.198</v>
+        <v>0.2514335787695359</v>
       </c>
       <c r="N44" t="n">
-        <v>0.432</v>
-      </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>within target band</t>
-        </is>
+        <v>0.1889508008028289</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.4358046681623484</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111542946/</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-60000-111780986</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>idealista_111266709</t>
+          <t>idealista_110658936</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3057,21 +3191,21 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Piso en Paseo de Francesc Macià, Coll Favà - Can Magí, Sant Cugat del Vallès</t>
+          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>599000</v>
+        <v>525000</v>
       </c>
       <c r="E45" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F45" t="n">
         <v>3</v>
       </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="n">
-        <v>13.46</v>
+        <v>50.2454108925926</v>
       </c>
       <c r="I45" t="n">
         <v>1</v>
@@ -3080,49 +3214,52 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0.752</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>0.266</v>
+        <v>0.6664285714285714</v>
       </c>
       <c r="M45" t="n">
-        <v>0.238</v>
+        <v>0.3000107511763098</v>
       </c>
       <c r="N45" t="n">
-        <v>0.431</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>within target band, good profile match</t>
-        </is>
+        <v>0.2878353144544138</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.434504043335217</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111266709/</t>
+          <t>within target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110658936/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-50386-111290686</t>
+          <t>idealista_111945069</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Piso en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
+          <t>Piso en Clota, De La, Volpelleres, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>620000</v>
+        <v>589000</v>
       </c>
       <c r="E46" t="n">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="F46" t="n">
         <v>3</v>
@@ -3131,7 +3268,7 @@
         <v>2</v>
       </c>
       <c r="H46" t="n">
-        <v>24.01</v>
+        <v>0.9851794111111111</v>
       </c>
       <c r="I46" t="n">
         <v>1</v>
@@ -3140,58 +3277,59 @@
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>0.587</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.318</v>
+        <v>0.7792857142857144</v>
       </c>
       <c r="M46" t="n">
-        <v>0.407</v>
+        <v>0.3053266235964196</v>
       </c>
       <c r="N46" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.006725340188478694</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.4318130707546299</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-50386-111290686</t>
+          <t>within target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111945069/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-56394-111496873</t>
+          <t>idealista_108411479</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ático en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
+          <t>Piso en Carretera de Vallvidrera, Parc Central - Colomer, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>565000</v>
+        <v>606000</v>
       </c>
       <c r="E47" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
-      </c>
-      <c r="G47" t="n">
-        <v>1</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="n">
-        <v>18.99</v>
+        <v>50.2454108925926</v>
       </c>
       <c r="I47" t="n">
         <v>1</v>
@@ -3200,58 +3338,61 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>0.831</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0.164</v>
+        <v>0.6971428571428572</v>
       </c>
       <c r="M47" t="n">
-        <v>0.321</v>
+        <v>0.268077582096018</v>
       </c>
       <c r="N47" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>within target band</t>
-        </is>
+        <v>0.2882862173612662</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.4312954620432365</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-56394-111496873</t>
+          <t>near target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/108411479/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>mashomes_ref-1133</t>
+          <t>yaencontre_inmueble-56057-111965775</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>mashomes</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sant Cugat del Vallès 1133</t>
+          <t>Piso en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>625000</v>
+        <v>545000</v>
       </c>
       <c r="E48" t="n">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="F48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G48" t="n">
         <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>28.14</v>
+        <v>7.055584503703704</v>
       </c>
       <c r="I48" t="n">
         <v>1</v>
@@ -3260,92 +3401,98 @@
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>0.548</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0.307</v>
+        <v>0.8235714285714285</v>
       </c>
       <c r="M48" t="n">
-        <v>0.481</v>
+        <v>0.2443966961954994</v>
       </c>
       <c r="N48" t="n">
-        <v>0.426</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.0720173855485458</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.4306305937645393</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>https://www.mashomes.es/es/venta/en-barcelona-sant_cugat_del_valles/ref-1133</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-56057-111965775</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>qgat_homes_ref-1683</t>
+          <t>yaencontre_inmueble-81822-111056938</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>qgat_homes</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Cases en venda a Sant Cugat del Vallès - La Floresta</t>
+          <t>Piso en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>620000</v>
+        <v>624000</v>
       </c>
       <c r="E49" t="n">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="F49" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G49" t="n">
         <v>1</v>
       </c>
       <c r="H49" t="n">
-        <v>28.19</v>
+        <v>63.13662617037037</v>
       </c>
       <c r="I49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49" t="n">
-        <v>0.587</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.256</v>
+        <v>0.5557142857142857</v>
       </c>
       <c r="M49" t="n">
-        <v>0.514</v>
+        <v>0.1820775610029042</v>
       </c>
       <c r="N49" t="n">
-        <v>0.424</v>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>near target band, good profile match</t>
-        </is>
+        <v>0.8251067907315626</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.4290271106182446</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>https://www.qgathomes.com/ca/venda/a-barcelona-sant_cugat_del_valles/ref-1683</t>
+          <t>near target band, long time online, 1 price cut(s)</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-81822-111056938</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>idealista_111543497</t>
+          <t>idealista_111372725</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3355,21 +3502,21 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Piso en Calle d'Aribau, Coll Favà - Can Magí, Sant Cugat del Vallès</t>
+          <t>Casa o chalet en Calle Marcos Redondo, Valldoreix, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>585000</v>
+        <v>589000</v>
       </c>
       <c r="E50" t="n">
-        <v>91</v>
+        <v>60</v>
       </c>
       <c r="F50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="n">
-        <v>11.11</v>
+        <v>52.58798033703704</v>
       </c>
       <c r="I50" t="n">
         <v>1</v>
@@ -3378,58 +3525,61 @@
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0.788</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.241</v>
+        <v>0.7792857142857144</v>
       </c>
       <c r="M50" t="n">
-        <v>0.198</v>
+        <v>0.1930600429903117</v>
       </c>
       <c r="N50" t="n">
-        <v>0.424</v>
-      </c>
-      <c r="O50" t="inlineStr">
+        <v>0.2987170268638044</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.4284598599013635</v>
+      </c>
+      <c r="P50" t="inlineStr">
         <is>
           <t>within target band, good profile match</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/111543497/</t>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111372725/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>fincas_calvo_pisos-sant-cugat-del-valles-centre-ref1468a-64211538549.120000</t>
+          <t>mashomes_ref-1133</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>fincas_calvo</t>
+          <t>mashomes</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Pisos en Sant Cugat del Vallès</t>
+          <t>Sant Cugat del Vallès 1133</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>510000</v>
+        <v>625000</v>
       </c>
       <c r="E51" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G51" t="n">
         <v>2</v>
       </c>
       <c r="H51" t="n">
-        <v>16.07</v>
+        <v>67.27564237407408</v>
       </c>
       <c r="I51" t="n">
         <v>1</v>
@@ -3438,58 +3588,61 @@
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0.549</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>0.382</v>
+        <v>0.5478571428571428</v>
       </c>
       <c r="M51" t="n">
-        <v>0.274</v>
+        <v>0.3174199051506082</v>
       </c>
       <c r="N51" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.4545765046561039</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.4276984951061044</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>https://fincascalvo.com/propiedad/pisos-sant-cugat-del-valles-centre-ref1468a-64211538549.120000/</t>
+          <t>near target band, long time online, strong size</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>https://www.mashomes.es/es/venta/en-barcelona-sant_cugat_del_valles/ref-1133</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>fincas_calvo_pisos-sant-cugat-del-valles-centre-ref1468-64184535809.120000</t>
+          <t>yaencontre_inmueble-56605-111305065</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>fincas_calvo</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Pisos en Sant Cugat del Vallès</t>
+          <t>Piso en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>510000</v>
+        <v>625000</v>
       </c>
       <c r="E52" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F52" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G52" t="n">
         <v>2</v>
       </c>
       <c r="H52" t="n">
-        <v>16.07</v>
+        <v>63.13662617037037</v>
       </c>
       <c r="I52" t="n">
         <v>1</v>
@@ -3498,58 +3651,61 @@
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0.549</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>0.382</v>
+        <v>0.5478571428571428</v>
       </c>
       <c r="M52" t="n">
-        <v>0.274</v>
+        <v>0.333573919767031</v>
       </c>
       <c r="N52" t="n">
-        <v>0.419</v>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.3869090630398294</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.4243330650025607</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>https://fincascalvo.com/propiedad/pisos-sant-cugat-del-valles-centre-ref1468-64184535809.120000/</t>
+          <t>near target band, long time online, strong size</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-56605-111305065</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-56605-111305065</t>
+          <t>idealista_110445435</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Piso en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
+          <t>Piso en Calle d'Álvarez, Arxius, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>625000</v>
+        <v>631000</v>
       </c>
       <c r="E53" t="n">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H53" t="n">
-        <v>24.01</v>
+        <v>50.2454108925926</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
@@ -3558,56 +3714,61 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0.548</v>
+        <v>1</v>
       </c>
       <c r="L53" t="n">
-        <v>0.322</v>
+        <v>0.5007142857142857</v>
       </c>
       <c r="M53" t="n">
-        <v>0.408</v>
+        <v>0.2777330218042988</v>
       </c>
       <c r="N53" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.2837145209889837</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.4194495181592929</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-56605-111305065</t>
+          <t>near target band, 1 reactivation(s), strong size</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110445435/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>idealista_111045661</t>
+          <t>yaencontre_inmueble-81822-107622727</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ático en Rovellat, Parc Central - Colomer, Sant Cugat del Vallès</t>
+          <t>Piso en L'Eixample, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>560000</v>
+        <v>625000</v>
       </c>
       <c r="E54" t="n">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G54" t="n">
+        <v>2</v>
+      </c>
       <c r="H54" t="n">
-        <v>11.11</v>
+        <v>63.13662617037037</v>
       </c>
       <c r="I54" t="n">
         <v>1</v>
@@ -3616,176 +3777,185 @@
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0.841</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>0.181</v>
+        <v>0.5478571428571428</v>
       </c>
       <c r="M54" t="n">
-        <v>0.195</v>
+        <v>0.3145633422153205</v>
       </c>
       <c r="N54" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>within target band</t>
-        </is>
+        <v>0.3860812066084544</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.4162244439661361</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111045661/</t>
+          <t>near target band, long time online, strong size</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-81822-107622727</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-49856-111132571</t>
+          <t>qgat_homes_ref-1784</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>qgat_homes</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ático en Mira-sol, Sant Cugat del Vallès</t>
+          <t>Àtic en venda a Sant Cugat del Vallès - Sant Domenec</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>660000</v>
+        <v>535000</v>
       </c>
       <c r="E55" t="n">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="F55" t="n">
         <v>3</v>
       </c>
       <c r="G55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>24.01</v>
+        <v>6.097309040740741</v>
       </c>
       <c r="I55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0.273</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0.319</v>
+        <v>0.7450000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>0.868</v>
+        <v>0.2614360781012138</v>
       </c>
       <c r="N55" t="n">
-        <v>0.413</v>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>near target band, 1 price cut(s), strong size</t>
-        </is>
+        <v>0.08839336950626878</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.4143149603300263</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-49856-111132571</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>https://www.qgathomes.com/ca/venda/a-barcelona-sant_cugat_del_valles/ref-1784</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>amat_casa-amb-encant-a-zona-mas-gener-de-mirasol</t>
+          <t>idealista_111965775</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>amat</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Casa amb encant, a zona Mas Gener de Mirasol</t>
+          <t>Piso en Dolors Bigas, Volpelleres, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>645000</v>
+        <v>545000</v>
       </c>
       <c r="E56" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="F56" t="n">
         <v>2</v>
       </c>
-      <c r="G56" t="n">
-        <v>1</v>
-      </c>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="n">
-        <v>28.19</v>
+        <v>7.055584503703704</v>
       </c>
       <c r="I56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0.391</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>0.185</v>
+        <v>0.8235714285714285</v>
       </c>
       <c r="M56" t="n">
-        <v>0.959</v>
+        <v>0.2121031988317033</v>
       </c>
       <c r="N56" t="n">
-        <v>0.412</v>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>near target band, 1 price cut(s), good profile match</t>
-        </is>
+        <v>0.04500951214432643</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.413016143861112</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>https://www.amatimmobiliaris.com/ca/venda/casa/barcelona/sant-cugat-del-valles/casa-amb-encant-a-zona-mas-gener-de-mirasol</t>
+          <t>within target band</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111965775/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>idealista_101690533</t>
+          <t>bachs_finques_descubre-este-espectacular-piso-en-sant-cugat-del-valles-en-la-tranquila-zona-de-vullpalleres</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>bachs_finques</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Torre en Can Roca, La Floresta, Sant Cugat del Vallès</t>
+          <t>¡Descubre este espectacular piso en Sant Cug...</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>650000</v>
+        <v>625000</v>
       </c>
       <c r="E57" t="n">
-        <v>289</v>
+        <v>95</v>
       </c>
       <c r="F57" t="n">
-        <v>6</v>
-      </c>
-      <c r="G57" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G57" t="n">
+        <v>2</v>
+      </c>
       <c r="H57" t="n">
-        <v>13.46</v>
+        <v>67.27564237407408</v>
       </c>
       <c r="I57" t="n">
         <v>1</v>
@@ -3794,58 +3964,59 @@
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0.351</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>0.532</v>
+        <v>0.5478571428571428</v>
       </c>
       <c r="M57" t="n">
-        <v>0.242</v>
+        <v>0.2802473963393947</v>
       </c>
       <c r="N57" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.4430200436369156</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.4103525722525164</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/101690533/</t>
+          <t>near target band, long time online, good profile match</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>https://www.finquesbachs.com/immoble/descubre-este-espectacular-piso-en-sant-cugat-del-valles-en-la-tranquila-zona-de-vullpalleres/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-81822-107622727</t>
+          <t>idealista_111070882</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Piso en L'Eixample, Sant Cugat del Vallès</t>
+          <t>Casa o chalet en Avenida del Montseny, La Floresta, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>625000</v>
+        <v>620000</v>
       </c>
       <c r="E58" t="n">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
-      </c>
-      <c r="G58" t="n">
-        <v>2</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="n">
-        <v>24.01</v>
+        <v>52.58798033703704</v>
       </c>
       <c r="I58" t="n">
         <v>1</v>
@@ -3854,58 +4025,59 @@
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0.548</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>0.306</v>
+        <v>0.5871428571428572</v>
       </c>
       <c r="M58" t="n">
-        <v>0.406</v>
+        <v>0.2996588667264406</v>
       </c>
       <c r="N58" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.2976927543922627</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.4096705821426635</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-81822-107622727</t>
+          <t>near target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111070882/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>bachs_finques_descubre-este-espectacular-piso-en-sant-cugat-del-valles-en-la-tranquila-zona-de-vullpalleres</t>
+          <t>idealista_110445422</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>bachs_finques</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>¡Descubre este espectacular piso en Sant Cug...</t>
+          <t>Casa o chalet independiente en Calle d'Astúries, Mirasol, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>625000</v>
+        <v>699000</v>
       </c>
       <c r="E59" t="n">
-        <v>95</v>
+        <v>306</v>
       </c>
       <c r="F59" t="n">
-        <v>3</v>
-      </c>
-      <c r="G59" t="n">
-        <v>2</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="n">
-        <v>28.14</v>
+        <v>50.2454108925926</v>
       </c>
       <c r="I59" t="n">
         <v>1</v>
@@ -3914,32 +4086,35 @@
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0.548</v>
+        <v>1</v>
       </c>
       <c r="L59" t="n">
-        <v>0.27</v>
+        <v>0.1114285714285714</v>
       </c>
       <c r="M59" t="n">
-        <v>0.487</v>
+        <v>0.547042441718073</v>
       </c>
       <c r="N59" t="n">
-        <v>0.411</v>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>near target band, good profile match</t>
-        </is>
+        <v>0.2899858527478497</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.4050358885726223</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>https://www.finquesbachs.com/immoble/descubre-este-espectacular-piso-en-sant-cugat-del-valles-en-la-tranquila-zona-de-vullpalleres/</t>
+          <t>near target band, 1 reactivation(s), strong size</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110445422/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>idealista_111372725</t>
+          <t>idealista_109332513</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3949,21 +4124,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Casa o chalet en Calle Marcos Redondo, Valldoreix, Sant Cugat del Vallès</t>
+          <t>Piso en CL Josep Irla, Can Matas, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>589000</v>
+        <v>625000</v>
       </c>
       <c r="E60" t="n">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="F60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="n">
-        <v>13.46</v>
+        <v>52.58798033703704</v>
       </c>
       <c r="I60" t="n">
         <v>1</v>
@@ -3972,174 +4147,185 @@
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0.779</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0.192</v>
+        <v>0.5478571428571428</v>
       </c>
       <c r="M60" t="n">
-        <v>0.235</v>
+        <v>0.3165704048285425</v>
       </c>
       <c r="N60" t="n">
-        <v>0.406</v>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>within target band, good profile match</t>
-        </is>
+        <v>0.3003461442402706</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.4042071509084617</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111372725/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/109332513/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>idealista_110658936</t>
+          <t>finques_soler_95</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>finques_soler</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
+          <t>89 m² y 4 habs</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>525000</v>
+        <v>495000</v>
       </c>
       <c r="E61" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="F61" t="n">
-        <v>3</v>
-      </c>
-      <c r="G61" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G61" t="n">
+        <v>2</v>
+      </c>
       <c r="H61" t="n">
-        <v>11.11</v>
+        <v>34.23700811481481</v>
       </c>
       <c r="I61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K61" t="n">
-        <v>0.666</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0.29</v>
+        <v>0.4307142857142857</v>
       </c>
       <c r="M61" t="n">
-        <v>0.197</v>
+        <v>0.3242823720215841</v>
       </c>
       <c r="N61" t="n">
-        <v>0.403</v>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.5357591768431794</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.4041009891628328</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/110658936/</t>
+          <t>within target band, 1 price cut(s), good profile match</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>https://solerfinques.com/propiedades/compra/viviendas/barcelona-province/barcelona/eixample/detalle/95</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>idealista_108411479</t>
+          <t>yaencontre_inmueble-51002-109330679</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Piso en Carretera de Vallvidrera, Parc Central - Colomer, Sant Cugat del Vallès</t>
+          <t>Piso en Mira-sol, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>606000</v>
+        <v>649000</v>
       </c>
       <c r="E62" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="F62" t="n">
         <v>3</v>
       </c>
-      <c r="G62" t="inlineStr"/>
+      <c r="G62" t="n">
+        <v>2</v>
+      </c>
       <c r="H62" t="n">
-        <v>11.11</v>
+        <v>63.13662617037037</v>
       </c>
       <c r="I62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>0.697</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
-        <v>0.26</v>
+        <v>0.3592857142857143</v>
       </c>
       <c r="M62" t="n">
-        <v>0.198</v>
+        <v>0.2792435688016824</v>
       </c>
       <c r="N62" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>near target band, good profile match</t>
-        </is>
+        <v>0.8112897989879195</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.4029428565607565</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/108411479/</t>
+          <t>near target band, long time online, 1 price cut(s)</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-51002-109330679</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-32348-111342226</t>
+          <t>idealista_111305065</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Piso en calle De Roc Codó en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
+          <t>Piso en Calle de Josep Irla, Can Matas, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>640800</v>
+        <v>625000</v>
       </c>
       <c r="E63" t="n">
-        <v>105</v>
+        <v>115</v>
       </c>
       <c r="F63" t="n">
         <v>3</v>
       </c>
-      <c r="G63" t="n">
-        <v>2</v>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="n">
-        <v>24.01</v>
+        <v>50.2454108925926</v>
       </c>
       <c r="I63" t="n">
         <v>1</v>
@@ -4148,32 +4334,35 @@
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0.424</v>
+        <v>0</v>
       </c>
       <c r="L63" t="n">
-        <v>0.378</v>
+        <v>0.5478571428571428</v>
       </c>
       <c r="M63" t="n">
-        <v>0.407</v>
+        <v>0.3165704048285425</v>
       </c>
       <c r="N63" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O63" t="inlineStr">
+        <v>0.2869902107056369</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.4022037608782667</v>
+      </c>
+      <c r="P63" t="inlineStr">
         <is>
           <t>near target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-32348-111342226</t>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111305065/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>idealista_110870946</t>
+          <t>idealista_111575503</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4183,73 +4372,84 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Piso en Calle Torre D´en Damians, 16, Hostafrancs, Barcelona</t>
+          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>464500</v>
-      </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+        <v>650000</v>
+      </c>
+      <c r="E64" t="n">
+        <v>120</v>
+      </c>
+      <c r="F64" t="n">
+        <v>4</v>
+      </c>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="n">
-        <v>13.46</v>
+        <v>50.24542246666667</v>
       </c>
       <c r="I64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0.191</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
-        <v>0.382</v>
+        <v>0.3514285714285714</v>
       </c>
       <c r="M64" t="n">
-        <v>0.777</v>
+        <v>0.4684037760555946</v>
       </c>
       <c r="N64" t="n">
-        <v>0.394</v>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>within target band, 1 price cut(s), good profile match</t>
-        </is>
+        <v>0.2842232161701267</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.4007372990418735</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/110870946/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111575503/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>tecnocasa_piso-en-venta-661224</t>
+          <t>yaencontre_inmueble-35254-111758804</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>tecnocasa</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Piso en venta</t>
+          <t>Ático en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>620000</v>
+        <v>619000</v>
       </c>
       <c r="E65" t="n">
-        <v>155</v>
-      </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
+        <v>104</v>
+      </c>
+      <c r="F65" t="n">
+        <v>3</v>
+      </c>
+      <c r="G65" t="n">
+        <v>2</v>
+      </c>
       <c r="H65" t="n">
-        <v>1.08</v>
+        <v>30.22449654074074</v>
       </c>
       <c r="I65" t="n">
         <v>1</v>
@@ -4258,56 +4458,61 @@
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0.587</v>
+        <v>0</v>
       </c>
       <c r="L65" t="n">
-        <v>0.411</v>
+        <v>0.595</v>
       </c>
       <c r="M65" t="n">
-        <v>0.014</v>
+        <v>0.3019887590892889</v>
       </c>
       <c r="N65" t="n">
-        <v>0.393</v>
-      </c>
-      <c r="O65" t="inlineStr">
+        <v>0.1999523152119526</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.3985809282008704</v>
+      </c>
+      <c r="P65" t="inlineStr">
         <is>
           <t>near target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>https://santcugat1.tecnocasa.es/sant-cugat-del-valles/piso-en-venta-661224</t>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-35254-111758804</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>idealista_111653164</t>
+          <t>yaencontre_inmueble-61648-111384331</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Piso en Volpelleres, Sant Cugat del Vallès</t>
+          <t>Piso en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>565000</v>
+        <v>640000</v>
       </c>
       <c r="E66" t="n">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="F66" t="n">
         <v>2</v>
       </c>
-      <c r="G66" t="inlineStr"/>
+      <c r="G66" t="n">
+        <v>2</v>
+      </c>
       <c r="H66" t="n">
-        <v>2.95</v>
+        <v>63.13662617037037</v>
       </c>
       <c r="I66" t="n">
         <v>1</v>
@@ -4316,58 +4521,59 @@
         <v>0</v>
       </c>
       <c r="K66" t="n">
-        <v>0.831</v>
+        <v>0</v>
       </c>
       <c r="L66" t="n">
-        <v>0.2</v>
+        <v>0.4299999999999999</v>
       </c>
       <c r="M66" t="n">
-        <v>0.055</v>
+        <v>0.3536808227522828</v>
       </c>
       <c r="N66" t="n">
-        <v>0.392</v>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>within target band</t>
-        </is>
+        <v>0.3867594480258602</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.393862664861414</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111653164/</t>
+          <t>near target band, long time online, strong size</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-61648-111384331</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-56985-111196843</t>
+          <t>idealista_108962462</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Piso en Parc Central - El Colomer - Pla de la Pagesa, Sant Cugat del Vallès</t>
+          <t>Casa o chalet independiente en Rambla Can Bell, Les Planes, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>654000</v>
+        <v>660000</v>
       </c>
       <c r="E67" t="n">
-        <v>165</v>
+        <v>233</v>
       </c>
       <c r="F67" t="n">
-        <v>4</v>
-      </c>
-      <c r="G67" t="n">
-        <v>2</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="G67" t="inlineStr"/>
       <c r="H67" t="n">
-        <v>24.01</v>
+        <v>50.2454108925926</v>
       </c>
       <c r="I67" t="n">
         <v>1</v>
@@ -4376,118 +4582,116 @@
         <v>0</v>
       </c>
       <c r="K67" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="L67" t="n">
-        <v>0.433</v>
+        <v>0.2728571428571429</v>
       </c>
       <c r="M67" t="n">
-        <v>0.408</v>
+        <v>0.5040908753746628</v>
       </c>
       <c r="N67" t="n">
-        <v>0.389</v>
-      </c>
-      <c r="O67" t="inlineStr">
+        <v>0.2900545554780654</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.3906720102235015</v>
+      </c>
+      <c r="P67" t="inlineStr">
         <is>
           <t>near target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-56985-111196843</t>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/108962462/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-55990-111085250</t>
+          <t>idealista_110870946</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
+          <t>Piso en Calle Torre D´en Damians, 16, Hostafrancs, Barcelona</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>650000</v>
-      </c>
-      <c r="E68" t="n">
-        <v>140</v>
-      </c>
-      <c r="F68" t="n">
-        <v>4</v>
-      </c>
-      <c r="G68" t="n">
-        <v>2</v>
-      </c>
+        <v>464500</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
       <c r="H68" t="n">
-        <v>24.01</v>
+        <v>52.59361691111111</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K68" t="n">
-        <v>0.351</v>
+        <v>0</v>
       </c>
       <c r="L68" t="n">
-        <v>0.407</v>
+        <v>0.1910714285714285</v>
       </c>
       <c r="M68" t="n">
-        <v>0.407</v>
+        <v>0.3877119260501649</v>
       </c>
       <c r="N68" t="n">
-        <v>0.388</v>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.7797356164218401</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.3882557249344929</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-55990-111085250</t>
+          <t>within target band, 1 price cut(s), good profile match</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110870946/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-61648-111384331</t>
+          <t>idealista_111758804</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Piso en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
+          <t>Ático en Calle de Roc Codó, Volpelleres, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>640000</v>
+        <v>619000</v>
       </c>
       <c r="E69" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F69" t="n">
-        <v>2</v>
-      </c>
-      <c r="G69" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G69" t="inlineStr"/>
       <c r="H69" t="n">
-        <v>24.01</v>
+        <v>30.22448496666667</v>
       </c>
       <c r="I69" t="n">
         <v>1</v>
@@ -4496,56 +4700,61 @@
         <v>0</v>
       </c>
       <c r="K69" t="n">
-        <v>0.43</v>
+        <v>0</v>
       </c>
       <c r="L69" t="n">
-        <v>0.346</v>
+        <v>0.595</v>
       </c>
       <c r="M69" t="n">
-        <v>0.406</v>
+        <v>0.2811627485444734</v>
       </c>
       <c r="N69" t="n">
-        <v>0.387</v>
-      </c>
-      <c r="O69" t="inlineStr">
+        <v>0.1737326693625859</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.3859010568946429</v>
+      </c>
+      <c r="P69" t="inlineStr">
         <is>
           <t>near target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-61648-111384331</t>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111758804/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>idealista_111070882</t>
+          <t>yaencontre_inmueble-32348-112022435</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Casa o chalet en Avenida del Montseny, La Floresta, Sant Cugat del Vallès</t>
+          <t>Piso en calle De Roc Codó en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>620000</v>
+        <v>628800</v>
       </c>
       <c r="E70" t="n">
-        <v>79</v>
+        <v>105</v>
       </c>
       <c r="F70" t="n">
-        <v>4</v>
-      </c>
-      <c r="G70" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G70" t="n">
+        <v>2</v>
+      </c>
       <c r="H70" t="n">
-        <v>13.46</v>
+        <v>0.9851794111111111</v>
       </c>
       <c r="I70" t="n">
         <v>1</v>
@@ -4554,32 +4763,35 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>0.587</v>
+        <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>0.292</v>
+        <v>0.518</v>
       </c>
       <c r="M70" t="n">
-        <v>0.239</v>
+        <v>0.3907737620300005</v>
       </c>
       <c r="N70" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>near target band, good profile match</t>
-        </is>
+        <v>0.03459215684025312</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.3856566056802143</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111070882/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-32348-112022435</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-625-110686849</t>
+          <t>yaencontre_inmueble-55261-110445435</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4589,127 +4801,131 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Piso en Valldoreix, Sant Cugat del Vallès</t>
+          <t>Piso en Parc Central - El Colomer - Pla de la Pagesa, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>470000</v>
+        <v>631000</v>
       </c>
       <c r="E71" t="n">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="F71" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G71" t="n">
         <v>1</v>
       </c>
       <c r="H71" t="n">
-        <v>24.01</v>
+        <v>63.13662617037037</v>
       </c>
       <c r="I71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J71" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>0.234</v>
+        <v>0</v>
       </c>
       <c r="L71" t="n">
-        <v>0.289</v>
+        <v>0.5007142857142857</v>
       </c>
       <c r="M71" t="n">
-        <v>0.854</v>
+        <v>0.2777330218042988</v>
       </c>
       <c r="N71" t="n">
-        <v>0.383</v>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>within target band, 1 price cut(s), good profile match</t>
-        </is>
+        <v>0.3864606946549276</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.3852554897433351</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-625-110686849</t>
+          <t>near target band, long time online, strong size</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-55261-110445435</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-49847-111279510</t>
+          <t>idealista_111493130</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Piso en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
+          <t>Piso en Volpelleres, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>698000</v>
+        <v>650000</v>
       </c>
       <c r="E72" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F72" t="n">
         <v>3</v>
       </c>
-      <c r="G72" t="n">
-        <v>2</v>
-      </c>
+      <c r="G72" t="inlineStr"/>
       <c r="H72" t="n">
-        <v>24.01</v>
+        <v>50.2454108925926</v>
       </c>
       <c r="I72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J72" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K72" t="n">
-        <v>0.114</v>
+        <v>1</v>
       </c>
       <c r="L72" t="n">
-        <v>0.38</v>
+        <v>0.3514285714285714</v>
       </c>
       <c r="M72" t="n">
-        <v>0.856</v>
+        <v>0.3124592912678945</v>
       </c>
       <c r="N72" t="n">
-        <v>0.382</v>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>near target band, 1 price cut(s), strong size</t>
-        </is>
+        <v>0.2841885645414048</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.3848413721525805</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-49847-111279510</t>
+          <t>near target band, 1 reactivation(s), strong size</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111493130/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>idealista_111290686</t>
+          <t>yaencontre_inmueble-49856-112027698</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Piso en Calle de Ramon Mas, Volpelleres, Sant Cugat del Vallès</t>
+          <t>Ático en Mira-sol, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -4721,9 +4937,11 @@
       <c r="F73" t="n">
         <v>3</v>
       </c>
-      <c r="G73" t="inlineStr"/>
+      <c r="G73" t="n">
+        <v>2</v>
+      </c>
       <c r="H73" t="n">
-        <v>11.11</v>
+        <v>0.01285302222222222</v>
       </c>
       <c r="I73" t="n">
         <v>1</v>
@@ -4732,58 +4950,59 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>0.587</v>
+        <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>0.301</v>
+        <v>0.5871428571428572</v>
       </c>
       <c r="M73" t="n">
-        <v>0.198</v>
+        <v>0.3347006858316731</v>
       </c>
       <c r="N73" t="n">
-        <v>0.381</v>
-      </c>
-      <c r="O73" t="inlineStr">
+        <v>0.02634942798416842</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.383686647205647</v>
+      </c>
+      <c r="P73" t="inlineStr">
         <is>
           <t>near target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/111290686/</t>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-49856-112027698</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-56985-111674115</t>
+          <t>idealista_111285485</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Piso en Torreblanca, Sant Cugat del Vallès</t>
+          <t>Casa o chalet independiente en Avenida del Montseny, La Floresta, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D74" t="n">
         <v>620000</v>
       </c>
       <c r="E74" t="n">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="F74" t="n">
-        <v>2</v>
-      </c>
-      <c r="G74" t="n">
         <v>3</v>
       </c>
+      <c r="G74" t="inlineStr"/>
       <c r="H74" t="n">
-        <v>1.08</v>
+        <v>52.58798033703704</v>
       </c>
       <c r="I74" t="n">
         <v>1</v>
@@ -4792,116 +5011,124 @@
         <v>0</v>
       </c>
       <c r="K74" t="n">
-        <v>0.587</v>
+        <v>0</v>
       </c>
       <c r="L74" t="n">
-        <v>0.381</v>
+        <v>0.5871428571428572</v>
       </c>
       <c r="M74" t="n">
-        <v>0.008</v>
+        <v>0.2365124693091177</v>
       </c>
       <c r="N74" t="n">
-        <v>0.379</v>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.2990527628986552</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.3833530965033468</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-56985-111674115</t>
+          <t>near target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111285485/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-55261-110445435</t>
+          <t>idealista_109330679</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Piso en Parc Central - El Colomer - Pla de la Pagesa, Sant Cugat del Vallès</t>
+          <t>Piso en Mirasol, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>631000</v>
+        <v>649000</v>
       </c>
       <c r="E75" t="n">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H75" t="n">
-        <v>24.01</v>
+        <v>52.59361691111111</v>
       </c>
       <c r="I75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K75" t="n">
-        <v>0.501</v>
+        <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>0.271</v>
+        <v>0.3592857142857143</v>
       </c>
       <c r="M75" t="n">
-        <v>0.406</v>
+        <v>0.2792435688016824</v>
       </c>
       <c r="N75" t="n">
-        <v>0.378</v>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.6728296844124085</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.3821738393744298</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-55261-110445435</t>
+          <t>near target band, 1 price cut(s), good profile match</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/109330679/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>idealista_109332513</t>
+          <t>yaencontre_inmueble-55990-111964186</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Piso en CL Josep Irla, Can Matas, Sant Cugat del Vallès</t>
+          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>625000</v>
+        <v>650000</v>
       </c>
       <c r="E76" t="n">
-        <v>115</v>
+        <v>140</v>
       </c>
       <c r="F76" t="n">
-        <v>3</v>
-      </c>
-      <c r="G76" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="G76" t="n">
+        <v>2</v>
+      </c>
       <c r="H76" t="n">
-        <v>13.46</v>
+        <v>7.055584503703704</v>
       </c>
       <c r="I76" t="n">
         <v>1</v>
@@ -4910,32 +5137,35 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>0.548</v>
+        <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>0.306</v>
+        <v>0.3514285714285714</v>
       </c>
       <c r="M76" t="n">
-        <v>0.238</v>
+        <v>0.5027058419108703</v>
       </c>
       <c r="N76" t="n">
-        <v>0.377</v>
-      </c>
-      <c r="O76" t="inlineStr">
+        <v>0.06206222095996008</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.3818200174195643</v>
+      </c>
+      <c r="P76" t="inlineStr">
         <is>
           <t>near target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/109332513/</t>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-55990-111964186</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>idealista_109163369</t>
+          <t>idealista_111003072</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -4945,21 +5175,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Chalet adosado en Sant Domènec, Sant Cugat del Vallès</t>
+          <t>Chalet adosado en Calle Marqués de Comillas, 125, Zona Esportiva, Terrassa</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>665000</v>
-      </c>
-      <c r="E77" t="n">
-        <v>184</v>
-      </c>
-      <c r="F77" t="n">
-        <v>5</v>
-      </c>
+        <v>494000</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="n">
-        <v>13.46</v>
+        <v>52.59361691111111</v>
       </c>
       <c r="I77" t="n">
         <v>1</v>
@@ -4968,32 +5194,35 @@
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>0.234</v>
+        <v>0</v>
       </c>
       <c r="L77" t="n">
-        <v>0.546</v>
+        <v>0.4228571428571429</v>
       </c>
       <c r="M77" t="n">
-        <v>0.241</v>
+        <v>0.3561653531151913</v>
       </c>
       <c r="N77" t="n">
-        <v>0.376</v>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.3067468391680964</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.3805471334280282</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/109163369/</t>
+          <t>within target band</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111003072/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-70970-111653164</t>
+          <t>yaencontre_inmueble-74661-111611520</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5003,23 +5232,23 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Piso en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
+          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>565000</v>
+        <v>630000</v>
       </c>
       <c r="E78" t="n">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="F78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H78" t="n">
-        <v>2.95</v>
+        <v>47.14117478148148</v>
       </c>
       <c r="I78" t="n">
         <v>1</v>
@@ -5028,58 +5257,59 @@
         <v>0</v>
       </c>
       <c r="K78" t="n">
-        <v>0.831</v>
+        <v>0</v>
       </c>
       <c r="L78" t="n">
-        <v>0.166</v>
+        <v>0.5085714285714287</v>
       </c>
       <c r="M78" t="n">
-        <v>0.043</v>
+        <v>0.2853693117429357</v>
       </c>
       <c r="N78" t="n">
-        <v>0.374</v>
-      </c>
-      <c r="O78" t="inlineStr">
-        <is>
-          <t>within target band</t>
-        </is>
+        <v>0.2947667183020425</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.377301492207487</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-70970-111653164</t>
+          <t>near target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-74661-111611520</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-49856-110966906</t>
+          <t>idealista_112022435</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
+          <t>Piso en Calle de Roc Codó, 20, Volpelleres, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>649000</v>
+        <v>628800</v>
       </c>
       <c r="E79" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F79" t="n">
         <v>3</v>
       </c>
-      <c r="G79" t="n">
-        <v>2</v>
-      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="n">
-        <v>24.01</v>
+        <v>0.9851794111111111</v>
       </c>
       <c r="I79" t="n">
         <v>1</v>
@@ -5088,32 +5318,35 @@
         <v>0</v>
       </c>
       <c r="K79" t="n">
-        <v>0.359</v>
+        <v>0</v>
       </c>
       <c r="L79" t="n">
-        <v>0.368</v>
+        <v>0.518</v>
       </c>
       <c r="M79" t="n">
-        <v>0.408</v>
+        <v>0.374648981713656</v>
       </c>
       <c r="N79" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="O79" t="inlineStr">
+        <v>0.008205059541915563</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.3749261333525991</v>
+      </c>
+      <c r="P79" t="inlineStr">
         <is>
           <t>near target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P79" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-49856-110966906</t>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/112022435/</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>idealista_111305065</t>
+          <t>idealista_110810595</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5123,21 +5356,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Piso en Calle de Josep Irla, Can Matas, Sant Cugat del Vallès</t>
+          <t>Casa o chalet independiente en Can Barata, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>625000</v>
+        <v>460000</v>
       </c>
       <c r="E80" t="n">
-        <v>115</v>
+        <v>192</v>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="n">
-        <v>11.11</v>
+        <v>50.2454108925926</v>
       </c>
       <c r="I80" t="n">
         <v>1</v>
@@ -5146,32 +5379,35 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>0.548</v>
+        <v>1</v>
       </c>
       <c r="L80" t="n">
-        <v>0.306</v>
+        <v>0.1557142857142857</v>
       </c>
       <c r="M80" t="n">
-        <v>0.198</v>
+        <v>0.4386127281057799</v>
       </c>
       <c r="N80" t="n">
-        <v>0.369</v>
-      </c>
-      <c r="O80" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.2910515997355448</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.3742695566178992</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111305065/</t>
+          <t>within target band, 1 reactivation(s), strong size</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110810595/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>idealista_110350807</t>
+          <t>idealista_112027698</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5181,55 +5417,58 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Casa o chalet independiente en Calle d'Andalusia, 8195, Mirasol, Sant Cugat del Vallès</t>
+          <t>Ático en Mirasol, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>645000</v>
+        <v>620000</v>
       </c>
       <c r="E81" t="n">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="F81" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G81" t="inlineStr"/>
       <c r="H81" t="n">
-        <v>11.11</v>
+        <v>0.008512744444444444</v>
       </c>
       <c r="I81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J81" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>0.391</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>0.239</v>
+        <v>0.5871428571428572</v>
       </c>
       <c r="M81" t="n">
-        <v>0.622</v>
+        <v>0.3202015645662952</v>
       </c>
       <c r="N81" t="n">
-        <v>0.369</v>
-      </c>
-      <c r="O81" t="inlineStr">
-        <is>
-          <t>near target band, 1 price cut(s), good profile match</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.373644602076563</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/110350807/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/112027698/</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>idealista_111337503</t>
+          <t>idealista_111611520</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5239,79 +5478,86 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Casa o chalet independiente en Calle d'Andalusia, Mirasol, Sant Cugat del Vallès</t>
+          <t>Piso en Calle de Clementina Arderiu, Coll Favà - Can Magí, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>645000</v>
+        <v>630000</v>
       </c>
       <c r="E82" t="n">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="F82" t="n">
-        <v>2</v>
-      </c>
-      <c r="G82" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G82" t="n">
+        <v>2</v>
+      </c>
       <c r="H82" t="n">
-        <v>13.46</v>
+        <v>47.14251737407407</v>
       </c>
       <c r="I82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" t="n">
-        <v>0.391</v>
+        <v>0</v>
       </c>
       <c r="L82" t="n">
-        <v>0.219</v>
+        <v>0.5085714285714287</v>
       </c>
       <c r="M82" t="n">
-        <v>0.665</v>
+        <v>0.2853693117429357</v>
       </c>
       <c r="N82" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="O82" t="inlineStr">
-        <is>
-          <t>near target band, 1 price cut(s), good profile match</t>
-        </is>
+        <v>0.2655262186798072</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.3729154172641517</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111337503/</t>
+          <t>near target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111611520/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>idealista_106551307</t>
+          <t>yaencontre_inmueble-35254-111976708</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Casa o chalet independiente en Calle d'Astúries, Mirasol, Sant Cugat del Vallès</t>
+          <t>Ático en Sant Domènec, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>699000</v>
+        <v>535000</v>
       </c>
       <c r="E83" t="n">
-        <v>421</v>
+        <v>71</v>
       </c>
       <c r="F83" t="n">
-        <v>6</v>
-      </c>
-      <c r="G83" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G83" t="n">
+        <v>1</v>
+      </c>
       <c r="H83" t="n">
-        <v>11.11</v>
+        <v>6.097309040740741</v>
       </c>
       <c r="I83" t="n">
         <v>1</v>
@@ -5320,37 +5566,40 @@
         <v>0</v>
       </c>
       <c r="K83" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="L83" t="n">
-        <v>0.643</v>
+        <v>0.7450000000000001</v>
       </c>
       <c r="M83" t="n">
-        <v>0.2</v>
+        <v>0.1650916141293333</v>
       </c>
       <c r="N83" t="n">
-        <v>0.368</v>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.06588900000852384</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.3704746300371748</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/106551307/</t>
+          <t>within target band</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-35254-111976708</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>idealista_111575503</t>
+          <t>yaencontre_inmueble-60224-111575503</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -5367,9 +5616,11 @@
       <c r="F84" t="n">
         <v>4</v>
       </c>
-      <c r="G84" t="inlineStr"/>
+      <c r="G84" t="n">
+        <v>2</v>
+      </c>
       <c r="H84" t="n">
-        <v>11.11</v>
+        <v>49.06857061481482</v>
       </c>
       <c r="I84" t="n">
         <v>1</v>
@@ -5378,58 +5629,61 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>0.351</v>
+        <v>0</v>
       </c>
       <c r="L84" t="n">
-        <v>0.456</v>
+        <v>0.3514285714285714</v>
       </c>
       <c r="M84" t="n">
-        <v>0.197</v>
+        <v>0.3897218779888107</v>
       </c>
       <c r="N84" t="n">
-        <v>0.367</v>
-      </c>
-      <c r="O84" t="inlineStr">
+        <v>0.3013298232566292</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.3702568929167996</v>
+      </c>
+      <c r="P84" t="inlineStr">
         <is>
           <t>near target band, strong size, good profile match</t>
         </is>
       </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/111575503/</t>
+      <c r="Q84" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-60224-111575503</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>idealista_110439991</t>
+          <t>qgat_homes_ref-1749</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>qgat_homes</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Casa o chalet en La Floresta, Sant Cugat del Vallès</t>
+          <t>Pis ideal inversors actualment amb llogater</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>620000</v>
+        <v>635000</v>
       </c>
       <c r="E85" t="n">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F85" t="n">
         <v>4</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H85" t="n">
-        <v>11.11</v>
+        <v>30.22449654074074</v>
       </c>
       <c r="I85" t="n">
         <v>1</v>
@@ -5438,90 +5692,98 @@
         <v>0</v>
       </c>
       <c r="K85" t="n">
-        <v>0.587</v>
+        <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>0.258</v>
+        <v>0.4692857142857143</v>
       </c>
       <c r="M85" t="n">
-        <v>0.199</v>
+        <v>0.3196014313631233</v>
       </c>
       <c r="N85" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="O85" t="inlineStr">
+        <v>0.2289606063249364</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.3688437799371141</v>
+      </c>
+      <c r="P85" t="inlineStr">
         <is>
           <t>near target band, good profile match</t>
         </is>
       </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/110439991/</t>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>https://www.qgathomes.com/ca/venda/a-barcelona-sant_cugat_del_valles/ref-1749</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>idealista_110686849</t>
+          <t>fincas_calvo_pisos-sant-cugat-del-valles-centre-ref1302-13401339538.120000</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>fincas_calvo</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Piso en Valldoreix, Sant Cugat del Vallès</t>
+          <t>Pisos en Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>470000</v>
+        <v>495000</v>
       </c>
       <c r="E86" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F86" t="n">
-        <v>4</v>
-      </c>
-      <c r="G86" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2</v>
+      </c>
       <c r="H86" t="n">
-        <v>13.46</v>
+        <v>41.24029515185185</v>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J86" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" t="n">
-        <v>0.234</v>
+        <v>0</v>
       </c>
       <c r="L86" t="n">
-        <v>0.323</v>
+        <v>0.4307142857142857</v>
       </c>
       <c r="M86" t="n">
-        <v>0.669</v>
+        <v>0.3270797826553337</v>
       </c>
       <c r="N86" t="n">
-        <v>0.361</v>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>within target band, 1 price cut(s), good profile match</t>
-        </is>
+        <v>0.2716706281014973</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.3656626193177551</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/110686849/</t>
+          <t>within target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q86" t="inlineStr">
+        <is>
+          <t>https://fincascalvo.com/propiedad/pisos-sant-cugat-del-valles-centre-ref1302-13401339538.120000/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>idealista_111285485</t>
+          <t>idealista_111056938</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5531,21 +5793,21 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Casa o chalet independiente en Avenida del Montseny, La Floresta, Sant Cugat del Vallès</t>
+          <t>Piso en Calle de Pere Calders, Volpelleres, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>620000</v>
+        <v>624000</v>
       </c>
       <c r="E87" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="F87" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="n">
-        <v>13.46</v>
+        <v>52.59361691111111</v>
       </c>
       <c r="I87" t="n">
         <v>1</v>
@@ -5554,58 +5816,61 @@
         <v>0</v>
       </c>
       <c r="K87" t="n">
-        <v>0.587</v>
+        <v>0</v>
       </c>
       <c r="L87" t="n">
-        <v>0.231</v>
+        <v>0.5557142857142857</v>
       </c>
       <c r="M87" t="n">
-        <v>0.239</v>
+        <v>0.2179200117687685</v>
       </c>
       <c r="N87" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="O87" t="inlineStr">
+        <v>0.2986564278137919</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0.365113385502242</v>
+      </c>
+      <c r="P87" t="inlineStr">
         <is>
           <t>near target band, good profile match</t>
         </is>
       </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>https://www.idealista.com/inmueble/111285485/</t>
+      <c r="Q87" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111056938/</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>tecnocasa_piso-en-venta-651578</t>
+          <t>idealista_111976708</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>tecnocasa</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Piso en venta</t>
+          <t>Ático en Paseo de Sant Magí, Sant Domènec, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>475000</v>
+        <v>535000</v>
       </c>
       <c r="E88" t="n">
-        <v>110</v>
+        <v>71</v>
       </c>
       <c r="F88" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>28.14</v>
+        <v>6.097309040740741</v>
       </c>
       <c r="I88" t="n">
         <v>1</v>
@@ -5614,32 +5879,35 @@
         <v>0</v>
       </c>
       <c r="K88" t="n">
-        <v>0.274</v>
+        <v>0</v>
       </c>
       <c r="L88" t="n">
-        <v>0.364</v>
+        <v>0.7450000000000001</v>
       </c>
       <c r="M88" t="n">
-        <v>0.486</v>
+        <v>0.1597752696653615</v>
       </c>
       <c r="N88" t="n">
-        <v>0.357</v>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>within target band, strong size, good profile match</t>
-        </is>
+        <v>0.03713275933952952</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.3639283292619575</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>https://santcugat1.tecnocasa.es/sant-cugat-del-valles/piso-en-venta-651578</t>
+          <t>within target band</t>
+        </is>
+      </c>
+      <c r="Q88" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111976708/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>idealista_108962462</t>
+          <t>idealista_109907963</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5649,21 +5917,21 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Casa o chalet independiente en Rambla Can Bell, Les Planes, Sant Cugat del Vallès</t>
+          <t>Casa o chalet independiente en Valldoreix, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>660000</v>
+        <v>671000</v>
       </c>
       <c r="E89" t="n">
-        <v>233</v>
+        <v>110</v>
       </c>
       <c r="F89" t="n">
         <v>5</v>
       </c>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="n">
-        <v>11.11</v>
+        <v>50.2454108925926</v>
       </c>
       <c r="I89" t="n">
         <v>1</v>
@@ -5672,56 +5940,61 @@
         <v>0</v>
       </c>
       <c r="K89" t="n">
-        <v>0.273</v>
+        <v>1</v>
       </c>
       <c r="L89" t="n">
-        <v>0.487</v>
+        <v>0.1914285714285714</v>
       </c>
       <c r="M89" t="n">
-        <v>0.201</v>
+        <v>0.384971676984027</v>
       </c>
       <c r="N89" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="O89" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.2837269846255527</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.3624273371659784</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/108962462/</t>
+          <t>near target band, 1 reactivation(s), strong size</t>
+        </is>
+      </c>
+      <c r="Q89" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/109907963/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>idealista_111085250</t>
+          <t>yaencontre_inmueble-77186-110587829</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Piso en Calle d'Adrià Gual, Coll Favà - Can Magí, Sant Cugat del Vallès</t>
+          <t>Piso en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>650000</v>
+        <v>484000</v>
       </c>
       <c r="E90" t="n">
-        <v>140</v>
+        <v>88</v>
       </c>
       <c r="F90" t="n">
-        <v>4</v>
-      </c>
-      <c r="G90" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G90" t="n">
+        <v>2</v>
+      </c>
       <c r="H90" t="n">
-        <v>13.46</v>
+        <v>63.13662617037037</v>
       </c>
       <c r="I90" t="n">
         <v>1</v>
@@ -5730,32 +6003,35 @@
         <v>0</v>
       </c>
       <c r="K90" t="n">
-        <v>0.351</v>
+        <v>0</v>
       </c>
       <c r="L90" t="n">
-        <v>0.407</v>
+        <v>0.3442857142857143</v>
       </c>
       <c r="M90" t="n">
-        <v>0.238</v>
+        <v>0.3415652424142616</v>
       </c>
       <c r="N90" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="O90" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.3897313951641016</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.360934198904467</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111085250/</t>
+          <t>within target band, long time online, good profile match</t>
+        </is>
+      </c>
+      <c r="Q90" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-77186-110587829</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>idealista_111003072</t>
+          <t>idealista_110041041</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5765,17 +6041,21 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chalet adosado en Calle Marqués de Comillas, 125, Zona Esportiva, Terrassa</t>
+          <t>Casa o chalet independiente en Rambla Can Bell, Les Planes, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>494000</v>
-      </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
+        <v>660000</v>
+      </c>
+      <c r="E91" t="n">
+        <v>233</v>
+      </c>
+      <c r="F91" t="n">
+        <v>3</v>
+      </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="n">
-        <v>13.46</v>
+        <v>50.2454108925926</v>
       </c>
       <c r="I91" t="n">
         <v>1</v>
@@ -5784,32 +6064,35 @@
         <v>0</v>
       </c>
       <c r="K91" t="n">
-        <v>0.423</v>
+        <v>0</v>
       </c>
       <c r="L91" t="n">
-        <v>0.349</v>
+        <v>0.2728571428571429</v>
       </c>
       <c r="M91" t="n">
-        <v>0.242</v>
+        <v>0.4263175155337085</v>
       </c>
       <c r="N91" t="n">
-        <v>0.354</v>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>within target band</t>
-        </is>
+        <v>0.2876342267358644</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.3576441497789706</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111003072/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q91" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/110041041/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-77186-110587829</t>
+          <t>yaencontre_inmueble-29493-110462885</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -5823,19 +6106,19 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>484000</v>
+        <v>687500</v>
       </c>
       <c r="E92" t="n">
-        <v>88</v>
+        <v>171</v>
       </c>
       <c r="F92" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G92" t="n">
         <v>2</v>
       </c>
       <c r="H92" t="n">
-        <v>24.01</v>
+        <v>63.13662617037037</v>
       </c>
       <c r="I92" t="n">
         <v>1</v>
@@ -5844,56 +6127,61 @@
         <v>0</v>
       </c>
       <c r="K92" t="n">
-        <v>0.344</v>
+        <v>0</v>
       </c>
       <c r="L92" t="n">
-        <v>0.333</v>
+        <v>0.1442857142857143</v>
       </c>
       <c r="M92" t="n">
-        <v>0.408</v>
+        <v>0.4836445673970128</v>
       </c>
       <c r="N92" t="n">
-        <v>0.352</v>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>within target band, good profile match</t>
-        </is>
+        <v>0.3890529724408993</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.3545057519887422</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-77186-110587829</t>
+          <t>near target band, long time online, strong size</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-29493-110462885</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>idealista_111342226</t>
+          <t>yaencontre_inmueble-56421-110208703</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Piso en Calle de Roc Codó, 50, Volpelleres, Sant Cugat del Vallès</t>
+          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>640800</v>
+        <v>659800</v>
       </c>
       <c r="E93" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F93" t="n">
         <v>3</v>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="n">
+        <v>2</v>
+      </c>
       <c r="H93" t="n">
-        <v>11.11</v>
+        <v>63.13662617037037</v>
       </c>
       <c r="I93" t="n">
         <v>1</v>
@@ -5902,58 +6190,59 @@
         <v>0</v>
       </c>
       <c r="K93" t="n">
-        <v>0.424</v>
+        <v>0</v>
       </c>
       <c r="L93" t="n">
-        <v>0.363</v>
+        <v>0.2744285714285714</v>
       </c>
       <c r="M93" t="n">
-        <v>0.197</v>
+        <v>0.3794178421772932</v>
       </c>
       <c r="N93" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="O93" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.3861694961901915</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.3532451488159967</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111342226/</t>
+          <t>near target band, long time online, strong size</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-56421-110208703</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-51945-111403113</t>
+          <t>idealista_111952768</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
+          <t>Casa o chalet independiente en Mirasol, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>650000</v>
+        <v>615000</v>
       </c>
       <c r="E94" t="n">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="F94" t="n">
-        <v>4</v>
-      </c>
-      <c r="G94" t="n">
-        <v>2</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G94" t="inlineStr"/>
       <c r="H94" t="n">
-        <v>24.01</v>
+        <v>8.207991911111112</v>
       </c>
       <c r="I94" t="n">
         <v>1</v>
@@ -5962,58 +6251,59 @@
         <v>0</v>
       </c>
       <c r="K94" t="n">
-        <v>0.351</v>
+        <v>0</v>
       </c>
       <c r="L94" t="n">
-        <v>0.325</v>
+        <v>0.6264285714285714</v>
       </c>
       <c r="M94" t="n">
-        <v>0.41</v>
+        <v>0.2246524105887759</v>
       </c>
       <c r="N94" t="n">
-        <v>0.351</v>
-      </c>
-      <c r="O94" t="inlineStr">
+        <v>0.04505715206748413</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.3532368159304132</v>
+      </c>
+      <c r="P94" t="inlineStr">
         <is>
           <t>near target band, good profile match</t>
         </is>
       </c>
-      <c r="P94" t="inlineStr">
-        <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-51945-111403113</t>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111952768/</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>aproperties_vsc2312001-casa-de-67-m2-con-terraza-aparcamiento-piscina-y-vistas-en-venta-en-valldoreix-sant-cugat-del-valles</t>
+          <t>idealista_109940600</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>aproperties</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Casa en venta en Valldoreix</t>
+          <t>Piso en Calle de Roc Codó, 37, Volpelleres, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>671000</v>
+        <v>660000</v>
       </c>
       <c r="E95" t="n">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="F95" t="n">
-        <v>5</v>
-      </c>
-      <c r="G95" t="n">
-        <v>2</v>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="n">
-        <v>28.14</v>
+        <v>50.2454108925926</v>
       </c>
       <c r="I95" t="n">
         <v>1</v>
@@ -6022,116 +6312,124 @@
         <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0.191</v>
+        <v>1</v>
       </c>
       <c r="L95" t="n">
-        <v>0.405</v>
+        <v>0.2728571428571429</v>
       </c>
       <c r="M95" t="n">
-        <v>0.489</v>
+        <v>0.2970340304894206</v>
       </c>
       <c r="N95" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="O95" t="inlineStr">
-        <is>
-          <t>near target band, good profile match</t>
-        </is>
+        <v>0.284024448029481</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.3524095737202615</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>https://www.aproperties.es/sant-cugat-del-valles/valldoreix/vsc2312001-casa-de-67-m2-con-terraza-aparcamiento-piscina-y-vistas-en-venta-en-valldoreix-sant-cugat-del-valles</t>
+          <t>near target band, 1 reactivation(s), strong size</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/109940600/</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>idealista_110670002</t>
+          <t>yaencontre_inmueble-55219-111493130</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>yaencontre</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
+          <t>Piso en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>655000</v>
+        <v>650000</v>
       </c>
       <c r="E96" t="n">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="F96" t="n">
         <v>3</v>
       </c>
-      <c r="G96" t="inlineStr"/>
+      <c r="G96" t="n">
+        <v>2</v>
+      </c>
       <c r="H96" t="n">
-        <v>11.11</v>
+        <v>58.12433450370371</v>
       </c>
       <c r="I96" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K96" t="n">
-        <v>0.312</v>
+        <v>0</v>
       </c>
       <c r="L96" t="n">
-        <v>0.252</v>
+        <v>0.3514285714285714</v>
       </c>
       <c r="M96" t="n">
-        <v>0.622</v>
+        <v>0.3269584125332723</v>
       </c>
       <c r="N96" t="n">
-        <v>0.347</v>
-      </c>
-      <c r="O96" t="inlineStr">
-        <is>
-          <t>near target band, 1 price cut(s), good profile match</t>
-        </is>
+        <v>0.3554341670065804</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.3520118889879662</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/110670002/</t>
+          <t>near target band, strong size, good profile match</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>https://www.yaencontre.com/venta/piso/inmueble-55219-111493130</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>idealista_109236700</t>
+          <t>aproperties_vsc2312001-casa-de-67-m2-con-terraza-aparcamiento-piscina-y-vistas-en-venta-en-valldoreix-sant-cugat-del-valles</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>aproperties</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chalet adosado en Sant Domènec, Sant Cugat del Vallès</t>
+          <t>Casa en venta en Valldoreix</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>654000</v>
+        <v>671000</v>
       </c>
       <c r="E97" t="n">
-        <v>165</v>
+        <v>67</v>
       </c>
       <c r="F97" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G97" t="n">
         <v>2</v>
       </c>
       <c r="H97" t="n">
-        <v>11.11</v>
+        <v>67.27564237407408</v>
       </c>
       <c r="I97" t="n">
         <v>1</v>
@@ -6140,56 +6438,61 @@
         <v>0</v>
       </c>
       <c r="K97" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="L97" t="n">
-        <v>0.433</v>
+        <v>0.1914285714285714</v>
       </c>
       <c r="M97" t="n">
-        <v>0.197</v>
+        <v>0.4128325252736672</v>
       </c>
       <c r="N97" t="n">
-        <v>0.346</v>
-      </c>
-      <c r="O97" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.4406056733537402</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.348054742291006</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/109236700/</t>
+          <t>near target band, long time online, good profile match</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>https://www.aproperties.es/sant-cugat-del-valles/valldoreix/vsc2312001-casa-de-67-m2-con-terraza-aparcamiento-piscina-y-vistas-en-venta-en-valldoreix-sant-cugat-del-valles</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>idealista_111196843</t>
+          <t>finques_soler_99</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>idealista_local</t>
+          <t>finques_soler</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Piso en Parc Central - Colomer, Sant Cugat del Vallès</t>
+          <t>86 m² y 3 habs</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>654000</v>
+        <v>500000</v>
       </c>
       <c r="E98" t="n">
-        <v>165</v>
+        <v>86</v>
       </c>
       <c r="F98" t="n">
-        <v>4</v>
-      </c>
-      <c r="G98" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="G98" t="n">
+        <v>2</v>
+      </c>
       <c r="H98" t="n">
-        <v>11.11</v>
+        <v>21.35008681851852</v>
       </c>
       <c r="I98" t="n">
         <v>1</v>
@@ -6198,58 +6501,61 @@
         <v>0</v>
       </c>
       <c r="K98" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="L98" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="M98" t="n">
-        <v>0.198</v>
+        <v>0.2855350176011389</v>
       </c>
       <c r="N98" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="O98" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.1774794788926442</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.3470494313279511</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>https://www.idealista.com/inmueble/111196843/</t>
+          <t>within target band, good profile match</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>https://solerfinques.com/propiedades/compra/viviendas/barcelona-province/sant-cugat-del-valles/detalle/99</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-32348-106536631</t>
+          <t>fincas_cano_pujol_ref-6094</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>fincas_cano_pujol</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Piso en calle De Roc Codó en Can Mates - Volpelleres, Sant Cugat del Vallès</t>
+          <t>Sant Cugat del Vallès 6094</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>671900</v>
+        <v>699000</v>
       </c>
       <c r="E99" t="n">
-        <v>113</v>
+        <v>172</v>
       </c>
       <c r="F99" t="n">
         <v>4</v>
       </c>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H99" t="n">
-        <v>24.01</v>
+        <v>67.27564237407408</v>
       </c>
       <c r="I99" t="n">
         <v>1</v>
@@ -6258,58 +6564,59 @@
         <v>0</v>
       </c>
       <c r="K99" t="n">
-        <v>0.189</v>
+        <v>0</v>
       </c>
       <c r="L99" t="n">
-        <v>0.437</v>
+        <v>0.1114285714285714</v>
       </c>
       <c r="M99" t="n">
-        <v>0.409</v>
+        <v>0.4745032412267897</v>
       </c>
       <c r="N99" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="O99" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.4366577154896866</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.3469642493117094</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-32348-106536631</t>
+          <t>near target band, long time online, strong size</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>https://www.fincascanopujol.es/es/venta/en-barcelona-sant_cugat_del_valles/ref-6094</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>yaencontre_inmueble-56421-110208703</t>
+          <t>idealista_111309408</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>yaencontre</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Piso en Coll Favà - Can Magí, Sant Cugat del Vallès</t>
+          <t>Piso en Torreblanca, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>659800</v>
+        <v>683000</v>
       </c>
       <c r="E100" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F100" t="n">
         <v>3</v>
       </c>
-      <c r="G100" t="n">
-        <v>2</v>
-      </c>
+      <c r="G100" t="inlineStr"/>
       <c r="H100" t="n">
-        <v>24.01</v>
+        <v>50.2454108925926</v>
       </c>
       <c r="I100" t="n">
         <v>1</v>
@@ -6318,85 +6625,89 @@
         <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>0.274</v>
+        <v>1</v>
       </c>
       <c r="L100" t="n">
-        <v>0.369</v>
+        <v>0.1571428571428572</v>
       </c>
       <c r="M100" t="n">
-        <v>0.408</v>
+        <v>0.3739103722890076</v>
       </c>
       <c r="N100" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="O100" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.2859995681907468</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.3468081910145637</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>https://www.yaencontre.com/venta/piso/inmueble-56421-110208703</t>
+          <t>near target band, 1 reactivation(s), strong size</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111309408/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>fincas_cano_pujol_ref-6094</t>
+          <t>idealista_111691318</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>fincas_cano_pujol</t>
+          <t>idealista_local</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sant Cugat del Vallès 6094</t>
+          <t>Casa o chalet independiente en Calle de Galícia, Mirasol, Sant Cugat del Vallès</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>699000</v>
+        <v>695000</v>
       </c>
       <c r="E101" t="n">
-        <v>172</v>
+        <v>157</v>
       </c>
       <c r="F101" t="n">
         <v>4</v>
       </c>
-      <c r="G101" t="n">
-        <v>3</v>
-      </c>
+      <c r="G101" t="inlineStr"/>
       <c r="H101" t="n">
-        <v>28.14</v>
+        <v>37.23014468888889</v>
       </c>
       <c r="I101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K101" t="n">
-        <v>0.111</v>
+        <v>0</v>
       </c>
       <c r="L101" t="n">
-        <v>0.458</v>
+        <v>0.1228571428571429</v>
       </c>
       <c r="M101" t="n">
-        <v>0.493</v>
+        <v>0.4356824565017807</v>
       </c>
       <c r="N101" t="n">
-        <v>0.344</v>
-      </c>
-      <c r="O101" t="inlineStr">
-        <is>
-          <t>near target band, strong size, good profile match</t>
-        </is>
+        <v>0.5069679040391393</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.3449774765810522</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>https://www.fincascanopujol.es/es/venta/en-barcelona-sant_cugat_del_valles/ref-6094</t>
+          <t>near target band, 1 price cut(s), strong size</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>https://www.idealista.com/inmueble/111691318/</t>
         </is>
       </c>
     </row>
